--- a/datagolf/workbooks/StatCaddy_Field_latest.xlsx
+++ b/datagolf/workbooks/StatCaddy_Field_latest.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K107"/>
+  <dimension ref="A1:K92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,36 +476,36 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Zach Bauchou</t>
+          <t>Zac Blair</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.016</v>
+        <v>-0.335</v>
       </c>
       <c r="C2" t="n">
-        <v>0.823</v>
+        <v>0.323</v>
       </c>
       <c r="D2" t="n">
-        <v>0.164</v>
+        <v>0.329</v>
       </c>
       <c r="E2" t="n">
-        <v>0.164</v>
+        <v>0.115</v>
       </c>
       <c r="F2" t="n">
-        <v>0.03</v>
+        <v>0.08</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.02</v>
+        <v>0.02</v>
       </c>
       <c r="H2" t="n">
-        <v>0.37</v>
+        <v>0.19</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.04</v>
+        <v>0.02</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Bank of Utah Championship</t>
+          <t>Butterfield Bermuda Championship</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -517,36 +517,36 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Christiaan Bezuidenhout</t>
+          <t>Chandler Blanchet</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0.1729</v>
+        <v>0.048</v>
       </c>
       <c r="C3" t="n">
-        <v>0.28</v>
+        <v>0.323</v>
       </c>
       <c r="D3" t="n">
-        <v>0.4543</v>
+        <v>-0.1</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0886</v>
+        <v>-0.244</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1271</v>
+        <v>-0.326</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.05</v>
+        <v>-0.04</v>
       </c>
       <c r="H3" t="n">
-        <v>0.732</v>
+        <v>-0.62</v>
       </c>
       <c r="I3" t="n">
         <v>-0.04</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Bank of Utah Championship</t>
+          <t>Butterfield Bermuda Championship</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -558,36 +558,36 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Zac Blair</t>
+          <t>Rafael Campos</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-0.407</v>
+        <v>-0.151</v>
       </c>
       <c r="C4" t="n">
-        <v>0.823</v>
+        <v>0.323</v>
       </c>
       <c r="D4" t="n">
-        <v>0.309</v>
+        <v>-0.376</v>
       </c>
       <c r="E4" t="n">
-        <v>0.06</v>
+        <v>-0.397</v>
       </c>
       <c r="F4" t="n">
-        <v>0.096</v>
+        <v>-0.293</v>
       </c>
       <c r="G4" t="n">
-        <v>0.01</v>
+        <v>0.09</v>
       </c>
       <c r="H4" t="n">
-        <v>0.06</v>
+        <v>-1.22</v>
       </c>
       <c r="I4" t="n">
-        <v>0.01</v>
+        <v>0.12</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Bank of Utah Championship</t>
+          <t>Butterfield Bermuda Championship</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -599,36 +599,36 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Chandler Blanchet</t>
+          <t>Cameron Champ</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.178</v>
+        <v>0.306</v>
       </c>
       <c r="C5" t="n">
-        <v>0.823</v>
+        <v>0.323</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.002</v>
+        <v>-0.726</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.277</v>
+        <v>-0.285</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.322</v>
+        <v>-0.315</v>
       </c>
       <c r="G5" t="n">
-        <v>0.12</v>
+        <v>-0.04</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.42</v>
+        <v>-1.02</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.04</v>
+        <v>-0.06</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Bank of Utah Championship</t>
+          <t>Butterfield Bermuda Championship</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -640,36 +640,36 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Michael Brennan</t>
+          <t>Davis Chatfield</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.709</v>
+        <v>-0.469</v>
       </c>
       <c r="C6" t="n">
-        <v>0.823</v>
+        <v>0.323</v>
       </c>
       <c r="D6" t="n">
-        <v>0.338</v>
+        <v>-0.067</v>
       </c>
       <c r="E6" t="n">
-        <v>0.153</v>
+        <v>-0.1</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.214</v>
+        <v>-0.055</v>
       </c>
       <c r="G6" t="n">
         <v>0.02</v>
       </c>
       <c r="H6" t="n">
-        <v>0.99</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="I6" t="n">
-        <v>0.04</v>
+        <v>-0.04</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Bank of Utah Championship</t>
+          <t>Butterfield Bermuda Championship</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -681,36 +681,36 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Rafael Campos</t>
+          <t>Luke Clanton</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-0.228</v>
+        <v>-0.184</v>
       </c>
       <c r="C7" t="n">
-        <v>0.823</v>
+        <v>0.323</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.311</v>
+        <v>0.378</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.318</v>
+        <v>-0.07099999999999999</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.252</v>
+        <v>-0.095</v>
       </c>
       <c r="G7" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.11</v>
+        <v>0.03</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.01</v>
+        <v>-0.05</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Bank of Utah Championship</t>
+          <t>Butterfield Bermuda Championship</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -722,36 +722,36 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Davis Chatfield</t>
+          <t>Eric Cole</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-0.413</v>
+        <v>-0.318</v>
       </c>
       <c r="C8" t="n">
-        <v>0.823</v>
+        <v>0.323</v>
       </c>
       <c r="D8" t="n">
-        <v>0.07199999999999999</v>
+        <v>0.254</v>
       </c>
       <c r="E8" t="n">
-        <v>0.047</v>
+        <v>0.282</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.008999999999999999</v>
+        <v>0.241</v>
       </c>
       <c r="G8" t="n">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.3</v>
+        <v>0.46</v>
       </c>
       <c r="I8" t="n">
         <v>-0.04</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Bank of Utah Championship</t>
+          <t>Butterfield Bermuda Championship</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -763,36 +763,36 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Luke Clanton</t>
+          <t>Corey Conners</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-0.22</v>
+        <v>0.384</v>
       </c>
       <c r="C9" t="n">
-        <v>0.823</v>
+        <v>0.323</v>
       </c>
       <c r="D9" t="n">
-        <v>0.111</v>
+        <v>0.536</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.185</v>
+        <v>-0.094</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.106</v>
+        <v>-0.016</v>
       </c>
       <c r="G9" t="n">
-        <v>0.01</v>
+        <v>-0.14</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.4</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.03</v>
+        <v>-0.04</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Bank of Utah Championship</t>
+          <t>Butterfield Bermuda Championship</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -804,36 +804,36 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Eric Cole</t>
+          <t>Trace Crowe</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>-0.275</v>
+        <v>0.074</v>
       </c>
       <c r="C10" t="n">
-        <v>0.823</v>
+        <v>0.323</v>
       </c>
       <c r="D10" t="n">
-        <v>0.098</v>
+        <v>0.358</v>
       </c>
       <c r="E10" t="n">
-        <v>0.495</v>
+        <v>-0.022</v>
       </c>
       <c r="F10" t="n">
-        <v>0.269</v>
+        <v>-0.043</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.11</v>
+        <v>-0.01</v>
       </c>
       <c r="H10" t="n">
-        <v>0.59</v>
+        <v>0.37</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.04</v>
+        <v>-0.01</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Bank of Utah Championship</t>
+          <t>Butterfield Bermuda Championship</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -845,36 +845,36 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Pierceson Coody</t>
+          <t>Joel Dahmen</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.207</v>
+        <v>0.195</v>
       </c>
       <c r="C11" t="n">
-        <v>0.823</v>
+        <v>0.323</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.02</v>
+        <v>0.141</v>
       </c>
       <c r="E11" t="n">
-        <v>0.171</v>
+        <v>-0.498</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.065</v>
+        <v>-0.178</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.02</v>
+        <v>-0.09</v>
       </c>
       <c r="H11" t="n">
-        <v>0.29</v>
+        <v>-0.34</v>
       </c>
       <c r="I11" t="n">
-        <v>0.02</v>
+        <v>-0.05</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Bank of Utah Championship</t>
+          <t>Butterfield Bermuda Championship</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -886,36 +886,36 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Trace Crowe</t>
+          <t>Cam Davis</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.096</v>
+        <v>-0.605</v>
       </c>
       <c r="C12" t="n">
-        <v>0.823</v>
+        <v>0.323</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.032</v>
+        <v>-0.362</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.054</v>
+        <v>-0.169</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.104</v>
+        <v>-0.116</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.01</v>
+        <v>0.15</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.09</v>
+        <v>-1.25</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.02</v>
+        <v>-0.05</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Bank of Utah Championship</t>
+          <t>Butterfield Bermuda Championship</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -927,36 +927,36 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Joel Dahmen</t>
+          <t>Zecheng Dou</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.116</v>
+        <v>0.118</v>
       </c>
       <c r="C13" t="n">
-        <v>0.823</v>
+        <v>0.323</v>
       </c>
       <c r="D13" t="n">
-        <v>0.201</v>
+        <v>0.189</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.379</v>
+        <v>-0.167</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.185</v>
+        <v>-0.068</v>
       </c>
       <c r="G13" t="n">
-        <v>0.13</v>
+        <v>-0</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.25</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Bank of Utah Championship</t>
+          <t>Butterfield Bermuda Championship</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -968,36 +968,36 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Cam Davis</t>
+          <t>Adrien Dumont De Chassart</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>-0.664</v>
+        <v>-0.663</v>
       </c>
       <c r="C14" t="n">
-        <v>0.823</v>
+        <v>0.323</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.393</v>
+        <v>-0.155</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.104</v>
+        <v>0.305</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.105</v>
+        <v>0.215</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.06</v>
+        <v>0.14</v>
       </c>
       <c r="H14" t="n">
-        <v>-1.27</v>
+        <v>-0.3</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.04</v>
+        <v>0.03</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Bank of Utah Championship</t>
+          <t>Butterfield Bermuda Championship</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1009,36 +1009,36 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Zecheng Dou</t>
+          <t>Nick Dunlap</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.061</v>
+        <v>-1.168</v>
       </c>
       <c r="C15" t="n">
-        <v>0.823</v>
+        <v>0.323</v>
       </c>
       <c r="D15" t="n">
-        <v>0.059</v>
+        <v>-0.189</v>
       </c>
       <c r="E15" t="n">
-        <v>0.105</v>
+        <v>0.068</v>
       </c>
       <c r="F15" t="n">
-        <v>0.061</v>
+        <v>0.135</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.04</v>
+        <v>0.24</v>
       </c>
       <c r="H15" t="n">
-        <v>0.29</v>
+        <v>-1.15</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.04</v>
+        <v>-0.05</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Bank of Utah Championship</t>
+          <t>Butterfield Bermuda Championship</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1050,36 +1050,36 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Adrien Dumont De Chassart</t>
+          <t>Austin Eckroat</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-0.579</v>
+        <v>-0.045</v>
       </c>
       <c r="C16" t="n">
-        <v>0.823</v>
+        <v>0.323</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.276</v>
+        <v>0.206</v>
       </c>
       <c r="E16" t="n">
-        <v>0.316</v>
+        <v>0.118</v>
       </c>
       <c r="F16" t="n">
-        <v>0.179</v>
+        <v>-0.11</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.14</v>
+        <v>0.01</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.36</v>
+        <v>0.17</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.04</v>
+        <v>-0</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Bank of Utah Championship</t>
+          <t>Butterfield Bermuda Championship</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1091,36 +1091,36 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Nick Dunlap</t>
+          <t>A.J. Ewart</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>-1.113</v>
+        <v>-0.315</v>
       </c>
       <c r="C17" t="n">
-        <v>0.823</v>
+        <v>0.323</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.233</v>
+        <v>-0.08500000000000001</v>
       </c>
       <c r="E17" t="n">
-        <v>0.044</v>
+        <v>0.367</v>
       </c>
       <c r="F17" t="n">
-        <v>0.1</v>
+        <v>0.053</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.14</v>
+        <v>0.08</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.2</v>
+        <v>0.02</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.03</v>
+        <v>-0.04</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Bank of Utah Championship</t>
+          <t>Butterfield Bermuda Championship</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1132,36 +1132,36 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Austin Eckroat</t>
+          <t>Patrick Fishburn</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-0.044</v>
+        <v>0.148</v>
       </c>
       <c r="C18" t="n">
-        <v>0.823</v>
+        <v>0.323</v>
       </c>
       <c r="D18" t="n">
-        <v>0.205</v>
+        <v>-0.139</v>
       </c>
       <c r="E18" t="n">
-        <v>0.115</v>
+        <v>0.112</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.112</v>
+        <v>-0.06900000000000001</v>
       </c>
       <c r="G18" t="n">
         <v>-0.01</v>
       </c>
       <c r="H18" t="n">
-        <v>0.16</v>
+        <v>0.05</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.04</v>
+        <v>0.01</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Bank of Utah Championship</t>
+          <t>Butterfield Bermuda Championship</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1173,36 +1173,36 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A.J. Ewart</t>
+          <t>David Ford</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>-0.409</v>
+        <v>0.494</v>
       </c>
       <c r="C19" t="n">
-        <v>0.823</v>
+        <v>0.323</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.125</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E19" t="n">
-        <v>0.239</v>
+        <v>0.035</v>
       </c>
       <c r="F19" t="n">
-        <v>0.017</v>
+        <v>-0.17</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.08</v>
+        <v>-0.12</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.28</v>
+        <v>0.43</v>
       </c>
       <c r="I19" t="n">
         <v>-0.04</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Bank of Utah Championship</t>
+          <t>Butterfield Bermuda Championship</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -1214,36 +1214,36 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Tony Finau</t>
+          <t>Dylan Frittelli</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>-0.182</v>
+        <v>-0.588</v>
       </c>
       <c r="C20" t="n">
-        <v>0.823</v>
+        <v>0.323</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.046</v>
+        <v>-0.677</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.21</v>
+        <v>-0.16</v>
       </c>
       <c r="F20" t="n">
-        <v>0.245</v>
+        <v>0.047</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.06</v>
+        <v>0.2</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.19</v>
+        <v>-1.38</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.04</v>
+        <v>-0.01</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Bank of Utah Championship</t>
+          <t>Butterfield Bermuda Championship</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -1255,36 +1255,36 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Patrick Fishburn</t>
+          <t>Brice Garnett</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.18</v>
+        <v>-0.16</v>
       </c>
       <c r="C21" t="n">
-        <v>0.823</v>
+        <v>0.323</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.116</v>
+        <v>-0.343</v>
       </c>
       <c r="E21" t="n">
+        <v>-0.07099999999999999</v>
+      </c>
+      <c r="F21" t="n">
         <v>-0.008999999999999999</v>
       </c>
-      <c r="F21" t="n">
-        <v>-0.056</v>
-      </c>
       <c r="G21" t="n">
-        <v>0.01</v>
+        <v>-0.01</v>
       </c>
       <c r="H21" t="n">
-        <v>-0</v>
+        <v>-0.58</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.04</v>
+        <v>0.03</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Bank of Utah Championship</t>
+          <t>Butterfield Bermuda Championship</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -1296,36 +1296,36 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Steven Fisk</t>
+          <t>Lucas Glover</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.23</v>
+        <v>-0.066</v>
       </c>
       <c r="C22" t="n">
-        <v>0.823</v>
+        <v>0.323</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.142</v>
+        <v>0.235</v>
       </c>
       <c r="E22" t="n">
-        <v>0.022</v>
+        <v>-0.636</v>
       </c>
       <c r="F22" t="n">
-        <v>0.036</v>
+        <v>-0.091</v>
       </c>
       <c r="G22" t="n">
-        <v>0.01</v>
+        <v>-0.04</v>
       </c>
       <c r="H22" t="n">
-        <v>0.15</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.05</v>
+        <v>-0.02</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Bank of Utah Championship</t>
+          <t>Butterfield Bermuda Championship</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -1337,36 +1337,36 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>David Ford</t>
+          <t>Will Gordon</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.359</v>
+        <v>-0.117</v>
       </c>
       <c r="C23" t="n">
-        <v>0.823</v>
+        <v>0.323</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.252</v>
+        <v>-0.366</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.135</v>
+        <v>-0.273</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.217</v>
+        <v>-0.235</v>
       </c>
       <c r="G23" t="n">
-        <v>0.1</v>
+        <v>0.03</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.24</v>
+        <v>-0.99</v>
       </c>
       <c r="I23" t="n">
-        <v>0.03</v>
+        <v>0.09</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Bank of Utah Championship</t>
+          <t>Butterfield Bermuda Championship</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -1378,36 +1378,36 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Brice Garnett</t>
+          <t>Max Greyserman</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>-0.284</v>
+        <v>0.3429</v>
       </c>
       <c r="C24" t="n">
-        <v>0.823</v>
+        <v>0.17</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.363</v>
+        <v>-0.6943</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.032</v>
+        <v>0.6657</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.093</v>
+        <v>-0.04</v>
       </c>
       <c r="G24" t="n">
-        <v>0.05</v>
+        <v>-0.02</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.77</v>
+        <v>-0.018</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.05</v>
+        <v>0.04</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Bank of Utah Championship</t>
+          <t>Butterfield Bermuda Championship</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -1419,36 +1419,36 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Doug Ghim</t>
+          <t>Emiliano Grillo</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.462</v>
+        <v>0.026</v>
       </c>
       <c r="C25" t="n">
-        <v>0.823</v>
+        <v>0.323</v>
       </c>
       <c r="D25" t="n">
-        <v>0.443</v>
+        <v>0.239</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.065</v>
+        <v>-0.122</v>
       </c>
       <c r="F25" t="n">
-        <v>0.137</v>
+        <v>-0.19</v>
       </c>
       <c r="G25" t="n">
-        <v>0.04</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="H25" t="n">
-        <v>0.98</v>
+        <v>-0.05</v>
       </c>
       <c r="I25" t="n">
         <v>-0.02</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Bank of Utah Championship</t>
+          <t>Butterfield Bermuda Championship</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -1460,36 +1460,36 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Lucas Glover</t>
+          <t>Adam Hadwin</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-0.016</v>
+        <v>-0.217</v>
       </c>
       <c r="C26" t="n">
-        <v>0.823</v>
+        <v>0.323</v>
       </c>
       <c r="D26" t="n">
-        <v>0.186</v>
+        <v>-0.283</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.572</v>
+        <v>-0.053</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.089</v>
+        <v>-0.135</v>
       </c>
       <c r="G26" t="n">
-        <v>0.12</v>
+        <v>0.08</v>
       </c>
       <c r="H26" t="n">
-        <v>-0.49</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="I26" t="n">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Bank of Utah Championship</t>
+          <t>Butterfield Bermuda Championship</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -1501,36 +1501,36 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Max Greyserman</t>
+          <t>Nick Hardy</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.07000000000000001</v>
+        <v>-0.008</v>
       </c>
       <c r="C27" t="n">
-        <v>0.823</v>
+        <v>0.323</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.112</v>
+        <v>-0.4</v>
       </c>
       <c r="E27" t="n">
-        <v>0.334</v>
+        <v>-0.193</v>
       </c>
       <c r="F27" t="n">
-        <v>0.093</v>
+        <v>-0.172</v>
       </c>
       <c r="G27" t="n">
-        <v>-0.09</v>
+        <v>0.06</v>
       </c>
       <c r="H27" t="n">
-        <v>0.39</v>
+        <v>-0.77</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.04</v>
+        <v>0</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Bank of Utah Championship</t>
+          <t>Butterfield Bermuda Championship</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -1542,36 +1542,36 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Emiliano Grillo</t>
+          <t>Harry Higgs</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.177</v>
+        <v>-0.222</v>
       </c>
       <c r="C28" t="n">
-        <v>0.823</v>
+        <v>0.323</v>
       </c>
       <c r="D28" t="n">
-        <v>0.094</v>
+        <v>-0.343</v>
       </c>
       <c r="E28" t="n">
-        <v>0.027</v>
+        <v>-0.152</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.079</v>
+        <v>-0.104</v>
       </c>
       <c r="G28" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="H28" t="n">
-        <v>0.22</v>
+        <v>-0.82</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.03</v>
+        <v>0.05</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>Bank of Utah Championship</t>
+          <t>Butterfield Bermuda Championship</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -1583,36 +1583,36 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Harry Hall</t>
+          <t>Kensei Hirata</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.171</v>
+        <v>-0.345</v>
       </c>
       <c r="C29" t="n">
-        <v>0.823</v>
+        <v>0.323</v>
       </c>
       <c r="D29" t="n">
-        <v>0.221</v>
+        <v>-0.669</v>
       </c>
       <c r="E29" t="n">
-        <v>0.282</v>
+        <v>-0.214</v>
       </c>
       <c r="F29" t="n">
-        <v>0.244</v>
+        <v>-0.089</v>
       </c>
       <c r="G29" t="n">
-        <v>-0.09</v>
+        <v>0.04</v>
       </c>
       <c r="H29" t="n">
-        <v>0.58</v>
+        <v>-1.32</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.01</v>
+        <v>-0.04</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>Bank of Utah Championship</t>
+          <t>Butterfield Bermuda Championship</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -1624,36 +1624,36 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Garrick Higgo</t>
+          <t>Lee Hodges</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.006</v>
+        <v>0.3175</v>
       </c>
       <c r="C30" t="n">
-        <v>0.823</v>
+        <v>0.15</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.514</v>
+        <v>0.0775</v>
       </c>
       <c r="E30" t="n">
-        <v>0.187</v>
+        <v>-0.145</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.12</v>
       </c>
       <c r="G30" t="n">
-        <v>-0.03</v>
+        <v>0.02</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.4</v>
+        <v>0.1</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.05</v>
+        <v>-0.02</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>Bank of Utah Championship</t>
+          <t>Butterfield Bermuda Championship</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -1665,36 +1665,36 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Joe Highsmith</t>
+          <t>Rico Hoey</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.239</v>
+        <v>0.513</v>
       </c>
       <c r="C31" t="n">
-        <v>0.823</v>
+        <v>0.323</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.162</v>
+        <v>0.288</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.097</v>
+        <v>-0.201</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.061</v>
+        <v>-0.036</v>
       </c>
       <c r="G31" t="n">
-        <v>-0.01</v>
+        <v>-0.1</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.5600000000000001</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="I31" t="n">
         <v>0.02</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>Bank of Utah Championship</t>
+          <t>Butterfield Bermuda Championship</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -1706,36 +1706,36 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Kensei Hirata</t>
+          <t>Charley Hoffman</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.336</v>
+        <v>-0.132</v>
       </c>
       <c r="C32" t="n">
-        <v>0.823</v>
+        <v>0.323</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.703</v>
+        <v>-0.443</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.202</v>
+        <v>-0.472</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.106</v>
+        <v>-0.189</v>
       </c>
       <c r="G32" t="n">
-        <v>0.06</v>
+        <v>0.08</v>
       </c>
       <c r="H32" t="n">
-        <v>-1.35</v>
+        <v>-1.24</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.04</v>
+        <v>-0.03</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Bank of Utah Championship</t>
+          <t>Butterfield Bermuda Championship</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -1747,36 +1747,36 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Lee Hodges</t>
+          <t>Tom Hoge</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.18</v>
+        <v>-0.2</v>
       </c>
       <c r="C33" t="n">
-        <v>0.823</v>
+        <v>0.1275</v>
       </c>
       <c r="D33" t="n">
-        <v>0.063</v>
+        <v>0.5029</v>
       </c>
       <c r="E33" t="n">
-        <v>0.034</v>
+        <v>-0.2643</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.109</v>
+        <v>-0.03</v>
       </c>
       <c r="G33" t="n">
-        <v>0.07000000000000001</v>
+        <v>-0.02</v>
       </c>
       <c r="H33" t="n">
-        <v>0.17</v>
+        <v>-0.4025</v>
       </c>
       <c r="I33" t="n">
-        <v>0.02</v>
+        <v>-0.04</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Bank of Utah Championship</t>
+          <t>Butterfield Bermuda Championship</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -1788,36 +1788,36 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Rico Hoey</t>
+          <t>Mark Hubbard</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.37</v>
+        <v>-0.24</v>
       </c>
       <c r="C34" t="n">
-        <v>0.823</v>
+        <v>0.323</v>
       </c>
       <c r="D34" t="n">
-        <v>0.18</v>
+        <v>-0.074</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.236</v>
+        <v>-0.185</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.038</v>
+        <v>-0.045</v>
       </c>
       <c r="G34" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="H34" t="n">
-        <v>0.28</v>
+        <v>-0.55</v>
       </c>
       <c r="I34" t="n">
-        <v>0.05</v>
+        <v>0.08</v>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Bank of Utah Championship</t>
+          <t>Butterfield Bermuda Championship</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -1829,36 +1829,36 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Tom Hoge</t>
+          <t>Mackenzie Hughes</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.335</v>
+        <v>-0.174</v>
       </c>
       <c r="C35" t="n">
-        <v>0.823</v>
+        <v>0.323</v>
       </c>
       <c r="D35" t="n">
-        <v>0.245</v>
+        <v>-0.275</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.126</v>
+        <v>0.272</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.07199999999999999</v>
+        <v>0.312</v>
       </c>
       <c r="G35" t="n">
-        <v>-0.01</v>
+        <v>0.08</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.29</v>
+        <v>0.14</v>
       </c>
       <c r="I35" t="n">
-        <v>-0</v>
+        <v>-0.06</v>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Bank of Utah Championship</t>
+          <t>Butterfield Bermuda Championship</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -1870,36 +1870,36 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Rasmus Hojgaard</t>
+          <t>Ben James</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.101</v>
+        <v>0.493</v>
       </c>
       <c r="C36" t="n">
-        <v>0.823</v>
+        <v>0.323</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.05</v>
+        <v>0.507</v>
       </c>
       <c r="E36" t="n">
-        <v>0.391</v>
+        <v>0.135</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.07199999999999999</v>
+        <v>0.142</v>
       </c>
       <c r="G36" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.14</v>
       </c>
       <c r="H36" t="n">
-        <v>0.37</v>
+        <v>1.28</v>
       </c>
       <c r="I36" t="n">
         <v>-0.04</v>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Bank of Utah Championship</t>
+          <t>Butterfield Bermuda Championship</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -1911,36 +1911,36 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Max Homa</t>
+          <t>Takumi Kanaya</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.095</v>
+        <v>-0.0167</v>
       </c>
       <c r="C37" t="n">
-        <v>0.823</v>
+        <v>0.1271</v>
       </c>
       <c r="D37" t="n">
-        <v>0.07199999999999999</v>
+        <v>-0.46</v>
       </c>
       <c r="E37" t="n">
-        <v>0.265</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="F37" t="n">
-        <v>0.038</v>
+        <v>0.3317</v>
       </c>
       <c r="G37" t="n">
-        <v>-0.05</v>
+        <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>0.47</v>
+        <v>-0.112</v>
       </c>
       <c r="I37" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Bank of Utah Championship</t>
+          <t>Butterfield Bermuda Championship</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -1952,36 +1952,36 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Billy Horschel</t>
+          <t>Jeffrey Kang</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.037</v>
+        <v>-0.163</v>
       </c>
       <c r="C38" t="n">
-        <v>0.823</v>
+        <v>0.323</v>
       </c>
       <c r="D38" t="n">
-        <v>0.238</v>
+        <v>-0.274</v>
       </c>
       <c r="E38" t="n">
-        <v>0.02</v>
+        <v>-0.339</v>
       </c>
       <c r="F38" t="n">
-        <v>-0.15</v>
+        <v>-0.006</v>
       </c>
       <c r="G38" t="n">
-        <v>0.01</v>
+        <v>0.12</v>
       </c>
       <c r="H38" t="n">
-        <v>0.15</v>
+        <v>-0.78</v>
       </c>
       <c r="I38" t="n">
-        <v>0.01</v>
+        <v>-0.04</v>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>Bank of Utah Championship</t>
+          <t>Butterfield Bermuda Championship</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -1993,36 +1993,36 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Beau Hossler</t>
+          <t>Chan Kim</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.079</v>
+        <v>-0.059</v>
       </c>
       <c r="C39" t="n">
-        <v>0.823</v>
+        <v>0.323</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.101</v>
+        <v>-0.078</v>
       </c>
       <c r="E39" t="n">
-        <v>0.314</v>
+        <v>-0.267</v>
       </c>
       <c r="F39" t="n">
-        <v>0.213</v>
+        <v>0.018</v>
       </c>
       <c r="G39" t="n">
-        <v>-0.05</v>
+        <v>-0.03</v>
       </c>
       <c r="H39" t="n">
-        <v>0.51</v>
+        <v>-0.39</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>Bank of Utah Championship</t>
+          <t>Butterfield Bermuda Championship</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -2034,36 +2034,36 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Mark Hubbard</t>
+          <t>Chris Kirk</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-0.054</v>
+        <v>0.144</v>
       </c>
       <c r="C40" t="n">
-        <v>0.823</v>
+        <v>0.323</v>
       </c>
       <c r="D40" t="n">
-        <v>0.08500000000000001</v>
+        <v>0.611</v>
       </c>
       <c r="E40" t="n">
-        <v>-0.364</v>
+        <v>-0.268</v>
       </c>
       <c r="F40" t="n">
-        <v>0.001</v>
+        <v>0.109</v>
       </c>
       <c r="G40" t="n">
-        <v>0.04</v>
+        <v>-0.04</v>
       </c>
       <c r="H40" t="n">
-        <v>-0.33</v>
+        <v>0.6</v>
       </c>
       <c r="I40" t="n">
         <v>-0.04</v>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>Bank of Utah Championship</t>
+          <t>Butterfield Bermuda Championship</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -2075,36 +2075,36 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Mackenzie Hughes</t>
+          <t>Patton Kizzire</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-0.181</v>
+        <v>-0.956</v>
       </c>
       <c r="C41" t="n">
-        <v>0.823</v>
+        <v>0.323</v>
       </c>
       <c r="D41" t="n">
-        <v>-0.226</v>
+        <v>-0.214</v>
       </c>
       <c r="E41" t="n">
-        <v>0.398</v>
+        <v>-0.093</v>
       </c>
       <c r="F41" t="n">
-        <v>0.344</v>
+        <v>0.136</v>
       </c>
       <c r="G41" t="n">
-        <v>-0.12</v>
+        <v>0.18</v>
       </c>
       <c r="H41" t="n">
-        <v>0.34</v>
+        <v>-1.13</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.04</v>
+        <v>-0.01</v>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>Bank of Utah Championship</t>
+          <t>Butterfield Bermuda Championship</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -2116,36 +2116,36 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Stephan Jaeger</t>
+          <t>Ben Kohles</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>-0.387</v>
+        <v>0.3875</v>
       </c>
       <c r="C42" t="n">
-        <v>0.823</v>
+        <v>0.724</v>
       </c>
       <c r="D42" t="n">
-        <v>0.004</v>
+        <v>0.495</v>
       </c>
       <c r="E42" t="n">
-        <v>0.238</v>
+        <v>0.58</v>
       </c>
       <c r="F42" t="n">
-        <v>0.229</v>
+        <v>0.0925</v>
       </c>
       <c r="G42" t="n">
-        <v>-0.13</v>
+        <v>0.03</v>
       </c>
       <c r="H42" t="n">
-        <v>0.08</v>
+        <v>1.49</v>
       </c>
       <c r="I42" t="n">
-        <v>0.07000000000000001</v>
+        <v>-0.04</v>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>Bank of Utah Championship</t>
+          <t>Butterfield Bermuda Championship</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -2157,36 +2157,36 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Ben James</t>
+          <t>Christo Lamprecht</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.461</v>
+        <v>-0.31</v>
       </c>
       <c r="C43" t="n">
-        <v>0.823</v>
+        <v>0.323</v>
       </c>
       <c r="D43" t="n">
-        <v>0.45</v>
+        <v>-1.169</v>
       </c>
       <c r="E43" t="n">
-        <v>0.075</v>
+        <v>-0.046</v>
       </c>
       <c r="F43" t="n">
-        <v>0.041</v>
+        <v>-0.035</v>
       </c>
       <c r="G43" t="n">
-        <v>0.05</v>
+        <v>0.16</v>
       </c>
       <c r="H43" t="n">
-        <v>1.03</v>
+        <v>-1.56</v>
       </c>
       <c r="I43" t="n">
-        <v>-0.04</v>
+        <v>0.01</v>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>Bank of Utah Championship</t>
+          <t>Butterfield Bermuda Championship</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -2198,36 +2198,36 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Takumi Kanaya</t>
+          <t>Hank Lebioda</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>-0.186</v>
+        <v>-0.304</v>
       </c>
       <c r="C44" t="n">
-        <v>0.823</v>
+        <v>0.323</v>
       </c>
       <c r="D44" t="n">
-        <v>-0.432</v>
+        <v>-0.032</v>
       </c>
       <c r="E44" t="n">
-        <v>0.231</v>
+        <v>-0.188</v>
       </c>
       <c r="F44" t="n">
-        <v>0.238</v>
+        <v>-0.055</v>
       </c>
       <c r="G44" t="n">
-        <v>0</v>
+        <v>0.09</v>
       </c>
       <c r="H44" t="n">
-        <v>-0.15</v>
+        <v>-0.58</v>
       </c>
       <c r="I44" t="n">
-        <v>-0.01</v>
+        <v>0.05</v>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>Bank of Utah Championship</t>
+          <t>Butterfield Bermuda Championship</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -2239,36 +2239,36 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Jeffrey Kang</t>
+          <t>Haotong Li</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>-0.283</v>
+        <v>0.176</v>
       </c>
       <c r="C45" t="n">
-        <v>0.823</v>
+        <v>0.323</v>
       </c>
       <c r="D45" t="n">
-        <v>-0.216</v>
+        <v>0.035</v>
       </c>
       <c r="E45" t="n">
-        <v>-0.338</v>
+        <v>-0.135</v>
       </c>
       <c r="F45" t="n">
-        <v>0.006</v>
+        <v>-0.235</v>
       </c>
       <c r="G45" t="n">
-        <v>-0.03</v>
+        <v>0.01</v>
       </c>
       <c r="H45" t="n">
-        <v>-0.83</v>
+        <v>-0.16</v>
       </c>
       <c r="I45" t="n">
         <v>-0.04</v>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>Bank of Utah Championship</t>
+          <t>Butterfield Bermuda Championship</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -2280,36 +2280,36 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Johnny Keefer</t>
+          <t>Luke List</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.325</v>
+        <v>-0.042</v>
       </c>
       <c r="C46" t="n">
-        <v>0.823</v>
+        <v>0.323</v>
       </c>
       <c r="D46" t="n">
-        <v>0.259</v>
+        <v>-0.5629999999999999</v>
       </c>
       <c r="E46" t="n">
-        <v>0.017</v>
+        <v>-0.148</v>
       </c>
       <c r="F46" t="n">
-        <v>-0.142</v>
+        <v>-0.268</v>
       </c>
       <c r="G46" t="n">
-        <v>0.01</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H46" t="n">
-        <v>0.46</v>
+        <v>-1.02</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.04</v>
+        <v>-0.02</v>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>Bank of Utah Championship</t>
+          <t>Butterfield Bermuda Championship</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -2321,36 +2321,36 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Chris Kirk</t>
+          <t>Justin Lower</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.07199999999999999</v>
+        <v>-0.203</v>
       </c>
       <c r="C47" t="n">
-        <v>0.823</v>
+        <v>0.323</v>
       </c>
       <c r="D47" t="n">
-        <v>0.531</v>
+        <v>-0.282</v>
       </c>
       <c r="E47" t="n">
-        <v>-0.31</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="F47" t="n">
-        <v>0.107</v>
+        <v>-0.03</v>
       </c>
       <c r="G47" t="n">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="H47" t="n">
-        <v>0.4</v>
+        <v>-0.44</v>
       </c>
       <c r="I47" t="n">
-        <v>-0.01</v>
+        <v>0.14</v>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>Bank of Utah Championship</t>
+          <t>Butterfield Bermuda Championship</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
@@ -2362,36 +2362,36 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Patton Kizzire</t>
+          <t>Peter Malnati</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>-0.791</v>
+        <v>-0.785</v>
       </c>
       <c r="C48" t="n">
-        <v>0.823</v>
+        <v>0.323</v>
       </c>
       <c r="D48" t="n">
-        <v>-0.356</v>
+        <v>-0.407</v>
       </c>
       <c r="E48" t="n">
-        <v>-0.174</v>
+        <v>0.233</v>
       </c>
       <c r="F48" t="n">
-        <v>0.146</v>
+        <v>0.074</v>
       </c>
       <c r="G48" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0.2</v>
       </c>
       <c r="H48" t="n">
-        <v>-1.17</v>
+        <v>-0.89</v>
       </c>
       <c r="I48" t="n">
-        <v>0.03</v>
+        <v>0.08</v>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>Bank of Utah Championship</t>
+          <t>Butterfield Bermuda Championship</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -2403,36 +2403,36 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Ben Kohles</t>
+          <t>Ben Martin</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.111</v>
+        <v>-0.209</v>
       </c>
       <c r="C49" t="n">
-        <v>0.823</v>
+        <v>0.323</v>
       </c>
       <c r="D49" t="n">
-        <v>0.342</v>
+        <v>-0.201</v>
       </c>
       <c r="E49" t="n">
-        <v>-0.08500000000000001</v>
+        <v>-0.336</v>
       </c>
       <c r="F49" t="n">
-        <v>-0.031</v>
+        <v>-0.1</v>
       </c>
       <c r="G49" t="n">
-        <v>0.1</v>
+        <v>0.04</v>
       </c>
       <c r="H49" t="n">
-        <v>0.34</v>
+        <v>-0.85</v>
       </c>
       <c r="I49" t="n">
-        <v>0.02</v>
+        <v>0.05</v>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>Bank of Utah Championship</t>
+          <t>Butterfield Bermuda Championship</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
@@ -2444,36 +2444,36 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Jackson Koivun</t>
+          <t>Denny McCarthy</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.5117</v>
+        <v>-0.3471</v>
       </c>
       <c r="C50" t="n">
-        <v>0.8167</v>
+        <v>0.2725</v>
       </c>
       <c r="D50" t="n">
-        <v>0.5483</v>
+        <v>0.1414</v>
       </c>
       <c r="E50" t="n">
-        <v>0.0617</v>
+        <v>0.5029</v>
       </c>
       <c r="F50" t="n">
-        <v>0.2267</v>
+        <v>-0.0557</v>
       </c>
       <c r="G50" t="n">
-        <v>-0.01</v>
+        <v>-0.03</v>
       </c>
       <c r="H50" t="n">
-        <v>1.436</v>
+        <v>-0.0225</v>
       </c>
       <c r="I50" t="n">
         <v>-0.04</v>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>Bank of Utah Championship</t>
+          <t>Butterfield Bermuda Championship</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -2485,36 +2485,36 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Christo Lamprecht</t>
+          <t>Max McGreevy</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>-0.247</v>
+        <v>0.165</v>
       </c>
       <c r="C51" t="n">
-        <v>0.823</v>
+        <v>0.323</v>
       </c>
       <c r="D51" t="n">
-        <v>-1.208</v>
+        <v>0.138</v>
       </c>
       <c r="E51" t="n">
-        <v>-0.131</v>
+        <v>-0.133</v>
       </c>
       <c r="F51" t="n">
-        <v>-0.06</v>
+        <v>-0.014</v>
       </c>
       <c r="G51" t="n">
         <v>-0.07000000000000001</v>
       </c>
       <c r="H51" t="n">
-        <v>-1.65</v>
+        <v>0.16</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.04</v>
+        <v>0.13</v>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>Bank of Utah Championship</t>
+          <t>Butterfield Bermuda Championship</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
@@ -2526,36 +2526,36 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Hank Lebioda</t>
+          <t>Troy Merritt</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>-0.346</v>
+        <v>-0.665</v>
       </c>
       <c r="C52" t="n">
-        <v>0.823</v>
+        <v>0.323</v>
       </c>
       <c r="D52" t="n">
-        <v>-0.007</v>
+        <v>-0.587</v>
       </c>
       <c r="E52" t="n">
-        <v>-0.213</v>
+        <v>0.12</v>
       </c>
       <c r="F52" t="n">
-        <v>-0.029</v>
+        <v>-0.011</v>
       </c>
       <c r="G52" t="n">
-        <v>-0.02</v>
+        <v>0.13</v>
       </c>
       <c r="H52" t="n">
-        <v>-0.59</v>
+        <v>-1.14</v>
       </c>
       <c r="I52" t="n">
-        <v>-0.04</v>
+        <v>0.04</v>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>Bank of Utah Championship</t>
+          <t>Butterfield Bermuda Championship</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
@@ -2567,36 +2567,36 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Haotong Li</t>
+          <t>Taylor Montgomery</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.21</v>
+        <v>-0.908</v>
       </c>
       <c r="C53" t="n">
-        <v>0.823</v>
+        <v>0.323</v>
       </c>
       <c r="D53" t="n">
-        <v>0.049</v>
+        <v>-0.384</v>
       </c>
       <c r="E53" t="n">
-        <v>-0.039</v>
+        <v>0.386</v>
       </c>
       <c r="F53" t="n">
-        <v>-0.239</v>
+        <v>0.176</v>
       </c>
       <c r="G53" t="n">
-        <v>0.01</v>
+        <v>0.22</v>
       </c>
       <c r="H53" t="n">
-        <v>-0.02</v>
+        <v>-0.73</v>
       </c>
       <c r="I53" t="n">
-        <v>-0.04</v>
+        <v>-0.01</v>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>Bank of Utah Championship</t>
+          <t>Butterfield Bermuda Championship</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
@@ -2608,36 +2608,36 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>David Lipsky</t>
+          <t>Taylor Moore</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>-0.378</v>
+        <v>-0.2433</v>
       </c>
       <c r="C54" t="n">
-        <v>0.823</v>
+        <v>0.0225</v>
       </c>
       <c r="D54" t="n">
+        <v>-0.6533</v>
+      </c>
+      <c r="E54" t="n">
         <v>-0.24</v>
       </c>
-      <c r="E54" t="n">
-        <v>-0.033</v>
-      </c>
       <c r="F54" t="n">
-        <v>0.098</v>
+        <v>0.09</v>
       </c>
       <c r="G54" t="n">
-        <v>-0</v>
+        <v>-0.01</v>
       </c>
       <c r="H54" t="n">
-        <v>-0.55</v>
+        <v>-0.865</v>
       </c>
       <c r="I54" t="n">
-        <v>0.01</v>
+        <v>-0.04</v>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>Bank of Utah Championship</t>
+          <t>Butterfield Bermuda Championship</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
@@ -2649,36 +2649,36 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Justin Lower</t>
+          <t>Henrik Norlander</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>-0.252</v>
+        <v>-0.55</v>
       </c>
       <c r="C55" t="n">
-        <v>0.823</v>
+        <v>0.323</v>
       </c>
       <c r="D55" t="n">
-        <v>-0.209</v>
+        <v>-0.174</v>
       </c>
       <c r="E55" t="n">
-        <v>-0.118</v>
+        <v>-0.361</v>
       </c>
       <c r="F55" t="n">
-        <v>-0.048</v>
+        <v>-0.166</v>
       </c>
       <c r="G55" t="n">
-        <v>0.03</v>
+        <v>0.1</v>
       </c>
       <c r="H55" t="n">
-        <v>-0.63</v>
+        <v>-1.25</v>
       </c>
       <c r="I55" t="n">
-        <v>0.04</v>
+        <v>0</v>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>Bank of Utah Championship</t>
+          <t>Butterfield Bermuda Championship</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
@@ -2690,36 +2690,36 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Peter Malnati</t>
+          <t>Andrew Novak</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>-0.738</v>
+        <v>0.238</v>
       </c>
       <c r="C56" t="n">
-        <v>0.823</v>
+        <v>0.323</v>
       </c>
       <c r="D56" t="n">
-        <v>-0.433</v>
+        <v>0.393</v>
       </c>
       <c r="E56" t="n">
-        <v>0.184</v>
+        <v>-0.217</v>
       </c>
       <c r="F56" t="n">
-        <v>0.161</v>
+        <v>0.169</v>
       </c>
       <c r="G56" t="n">
-        <v>-0.13</v>
+        <v>-0.03</v>
       </c>
       <c r="H56" t="n">
-        <v>-0.83</v>
+        <v>0.58</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.03</v>
+        <v>0.08</v>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>Bank of Utah Championship</t>
+          <t>Butterfield Bermuda Championship</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
@@ -2731,36 +2731,36 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Ben Martin</t>
+          <t>Pontus Nyholm</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>-0.24</v>
+        <v>-0.008</v>
       </c>
       <c r="C57" t="n">
-        <v>0.823</v>
+        <v>0.323</v>
       </c>
       <c r="D57" t="n">
-        <v>-0.123</v>
+        <v>-0.501</v>
       </c>
       <c r="E57" t="n">
-        <v>-0.313</v>
+        <v>-0.111</v>
       </c>
       <c r="F57" t="n">
-        <v>-0.092</v>
+        <v>-0.12</v>
       </c>
       <c r="G57" t="n">
-        <v>0.04</v>
+        <v>0.1</v>
       </c>
       <c r="H57" t="n">
-        <v>-0.77</v>
+        <v>-0.74</v>
       </c>
       <c r="I57" t="n">
-        <v>-0.03</v>
+        <v>-0.04</v>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>Bank of Utah Championship</t>
+          <t>Butterfield Bermuda Championship</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
@@ -2772,36 +2772,36 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Denny McCarthy</t>
+          <t>John Parry</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>-0.378</v>
+        <v>-0.0567</v>
       </c>
       <c r="C58" t="n">
-        <v>0.823</v>
+        <v>0.3514</v>
       </c>
       <c r="D58" t="n">
-        <v>0.04</v>
+        <v>0.3817</v>
       </c>
       <c r="E58" t="n">
-        <v>0.446</v>
+        <v>-0.0233</v>
       </c>
       <c r="F58" t="n">
-        <v>0.08500000000000001</v>
+        <v>0.375</v>
       </c>
       <c r="G58" t="n">
-        <v>-0.08</v>
+        <v>0.01</v>
       </c>
       <c r="H58" t="n">
-        <v>0.19</v>
+        <v>0.668</v>
       </c>
       <c r="I58" t="n">
         <v>-0.04</v>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>Bank of Utah Championship</t>
+          <t>Butterfield Bermuda Championship</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
@@ -2813,36 +2813,36 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Matt McCarty</t>
+          <t>Jeremy Paul</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>-0.208</v>
+        <v>-0.267</v>
       </c>
       <c r="C59" t="n">
-        <v>0.823</v>
+        <v>0.323</v>
       </c>
       <c r="D59" t="n">
-        <v>-0.04</v>
+        <v>-0.302</v>
       </c>
       <c r="E59" t="n">
-        <v>0.455</v>
+        <v>-0.151</v>
       </c>
       <c r="F59" t="n">
-        <v>-0.047</v>
+        <v>0.006</v>
       </c>
       <c r="G59" t="n">
-        <v>-0.03</v>
+        <v>0.11</v>
       </c>
       <c r="H59" t="n">
-        <v>0.16</v>
+        <v>-0.71</v>
       </c>
       <c r="I59" t="n">
-        <v>0.08</v>
+        <v>-0.02</v>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>Bank of Utah Championship</t>
+          <t>Butterfield Bermuda Championship</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
@@ -2854,36 +2854,36 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Max McGreevy</t>
+          <t>Matthieu Pavon</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.004</v>
+        <v>-0.003</v>
       </c>
       <c r="C60" t="n">
-        <v>0.823</v>
+        <v>0.323</v>
       </c>
       <c r="D60" t="n">
-        <v>0.128</v>
+        <v>-0.26</v>
       </c>
       <c r="E60" t="n">
-        <v>-0.207</v>
+        <v>0.051</v>
       </c>
       <c r="F60" t="n">
-        <v>0.028</v>
+        <v>-0.139</v>
       </c>
       <c r="G60" t="n">
-        <v>0.06</v>
+        <v>-0.02</v>
       </c>
       <c r="H60" t="n">
+        <v>-0.35</v>
+      </c>
+      <c r="I60" t="n">
         <v>-0.05</v>
       </c>
-      <c r="I60" t="n">
-        <v>0.05</v>
-      </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>Bank of Utah Championship</t>
+          <t>Butterfield Bermuda Championship</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
@@ -2895,36 +2895,36 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Maverick McNealy</t>
+          <t>Taylor Pendrith</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.116</v>
+        <v>0.1125</v>
       </c>
       <c r="C61" t="n">
-        <v>0.823</v>
+        <v>0.1044</v>
       </c>
       <c r="D61" t="n">
-        <v>0.145</v>
+        <v>-0.19</v>
       </c>
       <c r="E61" t="n">
-        <v>0.671</v>
+        <v>-0.38</v>
       </c>
       <c r="F61" t="n">
-        <v>0.301</v>
+        <v>0.0838</v>
       </c>
       <c r="G61" t="n">
-        <v>-0.11</v>
+        <v>0</v>
       </c>
       <c r="H61" t="n">
-        <v>1.23</v>
+        <v>-0.844</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.05</v>
+        <v>-0.04</v>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>Bank of Utah Championship</t>
+          <t>Butterfield Bermuda Championship</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
@@ -2936,36 +2936,36 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Mac Meissner</t>
+          <t>Paul Peterson</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.042</v>
+        <v>-0.517</v>
       </c>
       <c r="C62" t="n">
-        <v>0.823</v>
+        <v>0.323</v>
       </c>
       <c r="D62" t="n">
-        <v>0.169</v>
+        <v>0.016</v>
       </c>
       <c r="E62" t="n">
-        <v>0.193</v>
+        <v>-0.05</v>
       </c>
       <c r="F62" t="n">
-        <v>0.205</v>
+        <v>0.139</v>
       </c>
       <c r="G62" t="n">
-        <v>-0.03</v>
+        <v>0.03</v>
       </c>
       <c r="H62" t="n">
-        <v>0.61</v>
+        <v>-0.41</v>
       </c>
       <c r="I62" t="n">
-        <v>0.02</v>
+        <v>-0.02</v>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>Bank of Utah Championship</t>
+          <t>Butterfield Bermuda Championship</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
@@ -2977,36 +2977,36 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Taylor Moore</t>
+          <t>Chandler Phillips</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.083</v>
+        <v>0.1567</v>
       </c>
       <c r="C63" t="n">
-        <v>0.823</v>
+        <v>0.3886</v>
       </c>
       <c r="D63" t="n">
-        <v>-0.205</v>
+        <v>-0.1383</v>
       </c>
       <c r="E63" t="n">
-        <v>0.066</v>
+        <v>0.3417</v>
       </c>
       <c r="F63" t="n">
-        <v>0.116</v>
+        <v>0.5983000000000001</v>
       </c>
       <c r="G63" t="n">
-        <v>-0.05</v>
+        <v>-0.01</v>
       </c>
       <c r="H63" t="n">
-        <v>0.06</v>
+        <v>0.61</v>
       </c>
       <c r="I63" t="n">
-        <v>-0.05</v>
+        <v>-0.04</v>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>Bank of Utah Championship</t>
+          <t>Butterfield Bermuda Championship</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
@@ -3018,36 +3018,36 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>William Mouw</t>
+          <t>Aldrich Potgieter</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="C64" t="n">
-        <v>0.823</v>
+        <v>0</v>
       </c>
       <c r="D64" t="n">
-        <v>0.244</v>
+        <v>-0.7633</v>
       </c>
       <c r="E64" t="n">
-        <v>-0.172</v>
+        <v>0.1167</v>
       </c>
       <c r="F64" t="n">
-        <v>-0.121</v>
+        <v>-0.6833</v>
       </c>
       <c r="G64" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="H64" t="n">
-        <v>0.05</v>
+        <v>-1.878</v>
       </c>
       <c r="I64" t="n">
-        <v>-0.06</v>
+        <v>-0.01</v>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>Bank of Utah Championship</t>
+          <t>Butterfield Bermuda Championship</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
@@ -3059,36 +3059,36 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Rasmus Neergaard-Petersen</t>
+          <t>Seamus Power</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.179</v>
+        <v>-0.093</v>
       </c>
       <c r="C65" t="n">
-        <v>0.823</v>
+        <v>0.323</v>
       </c>
       <c r="D65" t="n">
-        <v>0.102</v>
+        <v>-0.274</v>
       </c>
       <c r="E65" t="n">
-        <v>0.026</v>
+        <v>0.346</v>
       </c>
       <c r="F65" t="n">
-        <v>-0.021</v>
+        <v>0.222</v>
       </c>
       <c r="G65" t="n">
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="H65" t="n">
-        <v>0.29</v>
+        <v>0.2</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.04</v>
+        <v>0.2</v>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>Bank of Utah Championship</t>
+          <t>Butterfield Bermuda Championship</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
@@ -3100,36 +3100,36 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Pontus Nyholm</t>
+          <t>Chad Ramey</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.05</v>
+        <v>-0.252</v>
       </c>
       <c r="C66" t="n">
-        <v>0.823</v>
+        <v>0.323</v>
       </c>
       <c r="D66" t="n">
-        <v>-0.411</v>
+        <v>-0.276</v>
       </c>
       <c r="E66" t="n">
-        <v>-0.015</v>
+        <v>0.24</v>
       </c>
       <c r="F66" t="n">
-        <v>-0.103</v>
+        <v>0.137</v>
       </c>
       <c r="G66" t="n">
-        <v>-0.06</v>
+        <v>0.04</v>
       </c>
       <c r="H66" t="n">
-        <v>-0.48</v>
+        <v>-0.15</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.04</v>
+        <v>-0</v>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>Bank of Utah Championship</t>
+          <t>Butterfield Bermuda Championship</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
@@ -3141,36 +3141,36 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>John Parry</t>
+          <t>Davis Riley</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.019</v>
+        <v>-0.516</v>
       </c>
       <c r="C67" t="n">
-        <v>0.823</v>
+        <v>0.323</v>
       </c>
       <c r="D67" t="n">
-        <v>0.279</v>
+        <v>-0.45</v>
       </c>
       <c r="E67" t="n">
-        <v>-0.133</v>
+        <v>0.383</v>
       </c>
       <c r="F67" t="n">
-        <v>0.121</v>
+        <v>-0.11</v>
       </c>
       <c r="G67" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="H67" t="n">
+        <v>-0.6899999999999999</v>
+      </c>
+      <c r="I67" t="n">
         <v>0.03</v>
       </c>
-      <c r="H67" t="n">
-        <v>0.29</v>
-      </c>
-      <c r="I67" t="n">
-        <v>-0.04</v>
-      </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>Bank of Utah Championship</t>
+          <t>Butterfield Bermuda Championship</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
@@ -3182,36 +3182,36 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Matthieu Pavon</t>
+          <t>Kevin Roy</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.34</v>
+        <v>0.4643</v>
       </c>
       <c r="C68" t="n">
-        <v>0.823</v>
+        <v>0.3575</v>
       </c>
       <c r="D68" t="n">
-        <v>-0.218</v>
+        <v>0.1929</v>
       </c>
       <c r="E68" t="n">
-        <v>-0.032</v>
+        <v>-0.2471</v>
       </c>
       <c r="F68" t="n">
-        <v>-0.15</v>
+        <v>-0.0871</v>
       </c>
       <c r="G68" t="n">
-        <v>0.05</v>
+        <v>0.01</v>
       </c>
       <c r="H68" t="n">
-        <v>-0.06</v>
+        <v>1.332</v>
       </c>
       <c r="I68" t="n">
-        <v>-0.04</v>
+        <v>-0.02</v>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>Bank of Utah Championship</t>
+          <t>Butterfield Bermuda Championship</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
@@ -3223,36 +3223,36 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Taylor Pendrith</t>
+          <t>Marcelo Rozo</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.221</v>
+        <v>-0.168</v>
       </c>
       <c r="C69" t="n">
-        <v>0.823</v>
+        <v>0.323</v>
       </c>
       <c r="D69" t="n">
-        <v>0.062</v>
+        <v>-0.62</v>
       </c>
       <c r="E69" t="n">
-        <v>-0.189</v>
+        <v>-0.451</v>
       </c>
       <c r="F69" t="n">
-        <v>-0.001</v>
+        <v>-0.381</v>
       </c>
       <c r="G69" t="n">
-        <v>-0</v>
+        <v>0.04</v>
       </c>
       <c r="H69" t="n">
-        <v>0.09</v>
+        <v>-1.62</v>
       </c>
       <c r="I69" t="n">
         <v>-0.04</v>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>Bank of Utah Championship</t>
+          <t>Butterfield Bermuda Championship</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
@@ -3264,36 +3264,36 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Marco Penge</t>
+          <t>Isaiah Salinda</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.464</v>
+        <v>0.166</v>
       </c>
       <c r="C70" t="n">
-        <v>0.823</v>
+        <v>0.323</v>
       </c>
       <c r="D70" t="n">
-        <v>0.129</v>
+        <v>-0.231</v>
       </c>
       <c r="E70" t="n">
-        <v>0.057</v>
+        <v>-0.451</v>
       </c>
       <c r="F70" t="n">
-        <v>-0.012</v>
+        <v>-0.232</v>
       </c>
       <c r="G70" t="n">
-        <v>-0.02</v>
+        <v>-0.03</v>
       </c>
       <c r="H70" t="n">
-        <v>0.64</v>
+        <v>-0.75</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.04</v>
+        <v>0</v>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>Bank of Utah Championship</t>
+          <t>Butterfield Bermuda Championship</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
@@ -3305,36 +3305,36 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Paul Peterson</t>
+          <t>Adam Schenk</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>-0.496</v>
+        <v>-0.484</v>
       </c>
       <c r="C71" t="n">
-        <v>0.823</v>
+        <v>0.323</v>
       </c>
       <c r="D71" t="n">
-        <v>-0.021</v>
+        <v>-0.576</v>
       </c>
       <c r="E71" t="n">
-        <v>-0.025</v>
+        <v>-0.058</v>
       </c>
       <c r="F71" t="n">
-        <v>0.104</v>
+        <v>-0.014</v>
       </c>
       <c r="G71" t="n">
-        <v>0.04</v>
+        <v>0.15</v>
       </c>
       <c r="H71" t="n">
-        <v>-0.44</v>
+        <v>-1.13</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.01</v>
+        <v>0.09</v>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>Bank of Utah Championship</t>
+          <t>Butterfield Bermuda Championship</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
@@ -3346,36 +3346,36 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Chandler Phillips</t>
+          <t>Neal Shipley</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>-0.124</v>
+        <v>0.627</v>
       </c>
       <c r="C72" t="n">
-        <v>0.823</v>
+        <v>0.323</v>
       </c>
       <c r="D72" t="n">
-        <v>-0.232</v>
+        <v>0.172</v>
       </c>
       <c r="E72" t="n">
-        <v>0.217</v>
+        <v>-0.192</v>
       </c>
       <c r="F72" t="n">
-        <v>0.257</v>
+        <v>-0.193</v>
       </c>
       <c r="G72" t="n">
-        <v>-0.03</v>
+        <v>-0.14</v>
       </c>
       <c r="H72" t="n">
-        <v>0.12</v>
+        <v>0.41</v>
       </c>
       <c r="I72" t="n">
         <v>-0.04</v>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>Bank of Utah Championship</t>
+          <t>Butterfield Bermuda Championship</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
@@ -3387,36 +3387,36 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Aldrich Potgieter</t>
+          <t>Greyson Sigg</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.413</v>
+        <v>-0.259</v>
       </c>
       <c r="C73" t="n">
-        <v>0.823</v>
+        <v>0.323</v>
       </c>
       <c r="D73" t="n">
-        <v>-0.242</v>
+        <v>0.022</v>
       </c>
       <c r="E73" t="n">
-        <v>-0.007</v>
+        <v>-0.301</v>
       </c>
       <c r="F73" t="n">
-        <v>-0.321</v>
+        <v>0.003</v>
       </c>
       <c r="G73" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="H73" t="n">
-        <v>-0.16</v>
+        <v>-0.54</v>
       </c>
       <c r="I73" t="n">
-        <v>-0.04</v>
+        <v>0.09</v>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>Bank of Utah Championship</t>
+          <t>Butterfield Bermuda Championship</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
@@ -3428,36 +3428,36 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Seamus Power</t>
+          <t>Ben Silverman</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>-0.249</v>
+        <v>-0.219</v>
       </c>
       <c r="C74" t="n">
-        <v>0.823</v>
+        <v>0.323</v>
       </c>
       <c r="D74" t="n">
-        <v>-0.153</v>
+        <v>-0.353</v>
       </c>
       <c r="E74" t="n">
-        <v>0.194</v>
+        <v>0.064</v>
       </c>
       <c r="F74" t="n">
-        <v>0.149</v>
+        <v>-0.034</v>
       </c>
       <c r="G74" t="n">
-        <v>-0.03</v>
+        <v>0.05</v>
       </c>
       <c r="H74" t="n">
-        <v>-0.06</v>
+        <v>-0.54</v>
       </c>
       <c r="I74" t="n">
-        <v>0</v>
+        <v>-0.05</v>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>Bank of Utah Championship</t>
+          <t>Butterfield Bermuda Championship</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
@@ -3469,36 +3469,36 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Andrew Putnam</t>
+          <t>David Skinns</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>-0.6889999999999999</v>
+        <v>-0.667</v>
       </c>
       <c r="C75" t="n">
-        <v>0.823</v>
+        <v>0.323</v>
       </c>
       <c r="D75" t="n">
-        <v>0.056</v>
+        <v>-0.124</v>
       </c>
       <c r="E75" t="n">
-        <v>0.253</v>
+        <v>-0.195</v>
       </c>
       <c r="F75" t="n">
-        <v>0.269</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="G75" t="n">
-        <v>-0.02</v>
+        <v>0.13</v>
       </c>
       <c r="H75" t="n">
-        <v>-0.11</v>
+        <v>-0.92</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.05</v>
+        <v>0.03</v>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>Bank of Utah Championship</t>
+          <t>Butterfield Bermuda Championship</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
@@ -3510,36 +3510,36 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Chad Ramey</t>
+          <t>Austin Smotherman</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>-0.261</v>
+        <v>0.424</v>
       </c>
       <c r="C76" t="n">
-        <v>0.823</v>
+        <v>0.323</v>
       </c>
       <c r="D76" t="n">
-        <v>-0.249</v>
+        <v>0.492</v>
       </c>
       <c r="E76" t="n">
-        <v>0.17</v>
+        <v>-0.238</v>
       </c>
       <c r="F76" t="n">
-        <v>0.123</v>
+        <v>-0.214</v>
       </c>
       <c r="G76" t="n">
-        <v>-0.04</v>
+        <v>-0.12</v>
       </c>
       <c r="H76" t="n">
-        <v>-0.22</v>
+        <v>0.46</v>
       </c>
       <c r="I76" t="n">
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>Bank of Utah Championship</t>
+          <t>Butterfield Bermuda Championship</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
@@ -3551,36 +3551,36 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Davis Riley</t>
+          <t>Hayden Springer</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>-0.602</v>
+        <v>-0.122</v>
       </c>
       <c r="C77" t="n">
-        <v>0.823</v>
+        <v>0.323</v>
       </c>
       <c r="D77" t="n">
-        <v>-0.502</v>
+        <v>-0.27</v>
       </c>
       <c r="E77" t="n">
-        <v>0.295</v>
+        <v>0.218</v>
       </c>
       <c r="F77" t="n">
-        <v>-0.003</v>
+        <v>-0.049</v>
       </c>
       <c r="G77" t="n">
-        <v>-0.12</v>
+        <v>0.06</v>
       </c>
       <c r="H77" t="n">
-        <v>-0.8100000000000001</v>
+        <v>-0.22</v>
       </c>
       <c r="I77" t="n">
-        <v>-0.04</v>
+        <v>0.02</v>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>Bank of Utah Championship</t>
+          <t>Butterfield Bermuda Championship</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
@@ -3592,36 +3592,36 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Patrick Rodgers</t>
+          <t>Jimmy Stanger</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>-0.152</v>
+        <v>-0.039</v>
       </c>
       <c r="C78" t="n">
-        <v>0.823</v>
+        <v>0.323</v>
       </c>
       <c r="D78" t="n">
-        <v>-0.305</v>
+        <v>-0.8129999999999999</v>
       </c>
       <c r="E78" t="n">
-        <v>0.168</v>
+        <v>-0.125</v>
       </c>
       <c r="F78" t="n">
-        <v>0.048</v>
+        <v>-0.117</v>
       </c>
       <c r="G78" t="n">
-        <v>-0.06</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H78" t="n">
-        <v>-0.24</v>
+        <v>-1.09</v>
       </c>
       <c r="I78" t="n">
-        <v>0.04</v>
+        <v>-0.04</v>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>Bank of Utah Championship</t>
+          <t>Butterfield Bermuda Championship</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
@@ -3633,36 +3633,36 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Kevin Roy</t>
+          <t>Kevin Streelman</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.178</v>
+        <v>-0.063</v>
       </c>
       <c r="C79" t="n">
-        <v>0.823</v>
+        <v>0.323</v>
       </c>
       <c r="D79" t="n">
-        <v>0.105</v>
+        <v>-0.125</v>
       </c>
       <c r="E79" t="n">
-        <v>0.013</v>
+        <v>0.081</v>
       </c>
       <c r="F79" t="n">
-        <v>0.08</v>
+        <v>-0.035</v>
       </c>
       <c r="G79" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="H79" t="n">
-        <v>0.38</v>
+        <v>-0.14</v>
       </c>
       <c r="I79" t="n">
-        <v>-0.04</v>
+        <v>-0.05</v>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>Bank of Utah Championship</t>
+          <t>Butterfield Bermuda Championship</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
@@ -3674,36 +3674,36 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Marcelo Rozo</t>
+          <t>Adam Svensson</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>-0.171</v>
+        <v>-0.401</v>
       </c>
       <c r="C80" t="n">
-        <v>0.823</v>
+        <v>0.323</v>
       </c>
       <c r="D80" t="n">
-        <v>-0.552</v>
+        <v>0.117</v>
       </c>
       <c r="E80" t="n">
-        <v>-0.454</v>
+        <v>-0.364</v>
       </c>
       <c r="F80" t="n">
-        <v>-0.345</v>
+        <v>0.013</v>
       </c>
       <c r="G80" t="n">
-        <v>0.11</v>
+        <v>0.06</v>
       </c>
       <c r="H80" t="n">
-        <v>-1.52</v>
+        <v>-0.63</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.04</v>
+        <v>-0</v>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>Bank of Utah Championship</t>
+          <t>Butterfield Bermuda Championship</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
@@ -3715,36 +3715,36 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Isaiah Salinda</t>
+          <t>Jesper Svensson</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.344</v>
+        <v>0.369</v>
       </c>
       <c r="C81" t="n">
-        <v>0.823</v>
+        <v>0.323</v>
       </c>
       <c r="D81" t="n">
-        <v>-0.113</v>
+        <v>-0.369</v>
       </c>
       <c r="E81" t="n">
-        <v>-0.471</v>
+        <v>-0.182</v>
       </c>
       <c r="F81" t="n">
-        <v>-0.225</v>
+        <v>-0.154</v>
       </c>
       <c r="G81" t="n">
-        <v>0.08</v>
+        <v>-0.02</v>
       </c>
       <c r="H81" t="n">
-        <v>-0.47</v>
+        <v>-0.34</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>Bank of Utah Championship</t>
+          <t>Butterfield Bermuda Championship</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
@@ -3756,36 +3756,36 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Gordon Sargent</t>
+          <t>Davis Thompson</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.264</v>
+        <v>0.1833</v>
       </c>
       <c r="C82" t="n">
-        <v>0.823</v>
+        <v>0.4629</v>
       </c>
       <c r="D82" t="n">
-        <v>-0.675</v>
+        <v>0.7483</v>
       </c>
       <c r="E82" t="n">
-        <v>-0.08500000000000001</v>
+        <v>-0.1183</v>
       </c>
       <c r="F82" t="n">
-        <v>0.041</v>
+        <v>-0.2583</v>
       </c>
       <c r="G82" t="n">
-        <v>-0.02</v>
+        <v>0.02</v>
       </c>
       <c r="H82" t="n">
-        <v>-0.46</v>
+        <v>0.8725000000000001</v>
       </c>
       <c r="I82" t="n">
-        <v>-0.03</v>
+        <v>-0.04</v>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>Bank of Utah Championship</t>
+          <t>Butterfield Bermuda Championship</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
@@ -3797,36 +3797,36 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Adam Schenk</t>
+          <t>Alejandro Tosti</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>-0.413</v>
+        <v>0.15</v>
       </c>
       <c r="C83" t="n">
-        <v>0.823</v>
+        <v>0.323</v>
       </c>
       <c r="D83" t="n">
-        <v>-0.385</v>
+        <v>-0.397</v>
       </c>
       <c r="E83" t="n">
-        <v>-0.078</v>
+        <v>-0.371</v>
       </c>
       <c r="F83" t="n">
-        <v>-0.12</v>
+        <v>-0.038</v>
       </c>
       <c r="G83" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H83" t="n">
+        <v>-0.66</v>
+      </c>
+      <c r="I83" t="n">
         <v>-0.04</v>
       </c>
-      <c r="H83" t="n">
-        <v>-1</v>
-      </c>
-      <c r="I83" t="n">
-        <v>-0.01</v>
-      </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>Bank of Utah Championship</t>
+          <t>Butterfield Bermuda Championship</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
@@ -3838,36 +3838,36 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Neal Shipley</t>
+          <t>Erik Van Rooyen</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.581</v>
+        <v>-0.074</v>
       </c>
       <c r="C84" t="n">
-        <v>0.823</v>
+        <v>0.323</v>
       </c>
       <c r="D84" t="n">
-        <v>-0.103</v>
+        <v>-0.305</v>
       </c>
       <c r="E84" t="n">
-        <v>-0.16</v>
+        <v>0.056</v>
       </c>
       <c r="F84" t="n">
-        <v>-0.196</v>
+        <v>-0.012</v>
       </c>
       <c r="G84" t="n">
-        <v>0.09</v>
+        <v>0.06</v>
       </c>
       <c r="H84" t="n">
-        <v>0.12</v>
+        <v>-0.34</v>
       </c>
       <c r="I84" t="n">
-        <v>-0.04</v>
+        <v>-0.01</v>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>Bank of Utah Championship</t>
+          <t>Butterfield Bermuda Championship</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
@@ -3879,36 +3879,36 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Ben Silverman</t>
+          <t>John VanDerLaan</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>-0.315</v>
+        <v>0.06</v>
       </c>
       <c r="C85" t="n">
-        <v>0.823</v>
+        <v>0.323</v>
       </c>
       <c r="D85" t="n">
-        <v>-0.283</v>
+        <v>-0.139</v>
       </c>
       <c r="E85" t="n">
-        <v>0.062</v>
+        <v>-0.189</v>
       </c>
       <c r="F85" t="n">
-        <v>-0.03</v>
+        <v>0.002</v>
       </c>
       <c r="G85" t="n">
-        <v>0</v>
+        <v>-0.01</v>
       </c>
       <c r="H85" t="n">
-        <v>-0.57</v>
+        <v>-0.27</v>
       </c>
       <c r="I85" t="n">
-        <v>0.03</v>
+        <v>-0</v>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>Bank of Utah Championship</t>
+          <t>Butterfield Bermuda Championship</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
@@ -3920,36 +3920,36 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>David Skinns</t>
+          <t>Kristoffer Ventura</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>-0.385</v>
+        <v>0.481</v>
       </c>
       <c r="C86" t="n">
-        <v>0.823</v>
+        <v>0.323</v>
       </c>
       <c r="D86" t="n">
-        <v>-0.097</v>
+        <v>0.06</v>
       </c>
       <c r="E86" t="n">
-        <v>-0.221</v>
+        <v>-0.08799999999999999</v>
       </c>
       <c r="F86" t="n">
-        <v>0.039</v>
+        <v>-0.053</v>
       </c>
       <c r="G86" t="n">
-        <v>-0.03</v>
+        <v>-0.09</v>
       </c>
       <c r="H86" t="n">
-        <v>-0.66</v>
+        <v>0.4</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.03</v>
+        <v>0.01</v>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>Bank of Utah Championship</t>
+          <t>Butterfield Bermuda Championship</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
@@ -3961,36 +3961,36 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Jordan Smith</t>
+          <t>Camilo Villegas</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.553</v>
+        <v>-0.996</v>
       </c>
       <c r="C87" t="n">
-        <v>0.823</v>
+        <v>0.323</v>
       </c>
       <c r="D87" t="n">
-        <v>0.266</v>
+        <v>-0.488</v>
       </c>
       <c r="E87" t="n">
-        <v>-0.11</v>
+        <v>0.032</v>
       </c>
       <c r="F87" t="n">
-        <v>-0.139</v>
+        <v>0.039</v>
       </c>
       <c r="G87" t="n">
-        <v>0.09</v>
+        <v>0.26</v>
       </c>
       <c r="H87" t="n">
-        <v>0.57</v>
+        <v>-1.41</v>
       </c>
       <c r="I87" t="n">
-        <v>-0.04</v>
+        <v>0.22</v>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>Bank of Utah Championship</t>
+          <t>Butterfield Bermuda Championship</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
@@ -4002,36 +4002,36 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Austin Smotherman</t>
+          <t>Danny Walker</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.225</v>
+        <v>-0.142</v>
       </c>
       <c r="C88" t="n">
-        <v>0.823</v>
+        <v>0.323</v>
       </c>
       <c r="D88" t="n">
-        <v>0.351</v>
+        <v>-0.249</v>
       </c>
       <c r="E88" t="n">
-        <v>-0.384</v>
+        <v>-0.183</v>
       </c>
       <c r="F88" t="n">
-        <v>-0.277</v>
+        <v>-0.06</v>
       </c>
       <c r="G88" t="n">
-        <v>0.12</v>
+        <v>0.1</v>
       </c>
       <c r="H88" t="n">
-        <v>-0.09</v>
+        <v>-0.63</v>
       </c>
       <c r="I88" t="n">
         <v>-0.04</v>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>Bank of Utah Championship</t>
+          <t>Butterfield Bermuda Championship</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
@@ -4043,36 +4043,36 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Hayden Springer</t>
+          <t>Vince Whaley</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>-0.104</v>
+        <v>-0.858</v>
       </c>
       <c r="C89" t="n">
-        <v>0.823</v>
+        <v>0.323</v>
       </c>
       <c r="D89" t="n">
-        <v>-0.248</v>
+        <v>-0.624</v>
       </c>
       <c r="E89" t="n">
-        <v>0.261</v>
+        <v>0.352</v>
       </c>
       <c r="F89" t="n">
-        <v>-0.028</v>
+        <v>0.174</v>
       </c>
       <c r="G89" t="n">
-        <v>-0.06</v>
+        <v>0.22</v>
       </c>
       <c r="H89" t="n">
-        <v>-0.12</v>
+        <v>-0.96</v>
       </c>
       <c r="I89" t="n">
-        <v>0.01</v>
+        <v>0.16</v>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>Bank of Utah Championship</t>
+          <t>Butterfield Bermuda Championship</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
@@ -4084,36 +4084,36 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Jimmy Stanger</t>
+          <t>Aaron Wise</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>-0.01</v>
+        <v>-0.324</v>
       </c>
       <c r="C90" t="n">
-        <v>0.823</v>
+        <v>0.323</v>
       </c>
       <c r="D90" t="n">
-        <v>-0.798</v>
+        <v>-0.275</v>
       </c>
       <c r="E90" t="n">
-        <v>-0.08400000000000001</v>
+        <v>-0.179</v>
       </c>
       <c r="F90" t="n">
-        <v>-0.11</v>
+        <v>-0.04</v>
       </c>
       <c r="G90" t="n">
-        <v>-0</v>
+        <v>0.08</v>
       </c>
       <c r="H90" t="n">
-        <v>-1</v>
+        <v>-0.82</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.04</v>
+        <v>0.05</v>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>Bank of Utah Championship</t>
+          <t>Butterfield Bermuda Championship</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
@@ -4125,36 +4125,36 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Kevin Streelman</t>
+          <t>Dylan Wu</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>-0.114</v>
+        <v>-0.371</v>
       </c>
       <c r="C91" t="n">
-        <v>0.823</v>
+        <v>0.323</v>
       </c>
       <c r="D91" t="n">
-        <v>-0.271</v>
+        <v>-0.228</v>
       </c>
       <c r="E91" t="n">
-        <v>-0.152</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="F91" t="n">
-        <v>-0.109</v>
+        <v>0.06</v>
       </c>
       <c r="G91" t="n">
-        <v>0.04</v>
+        <v>0.08</v>
       </c>
       <c r="H91" t="n">
-        <v>-0.65</v>
+        <v>-0.45</v>
       </c>
       <c r="I91" t="n">
-        <v>0.02</v>
+        <v>0.1</v>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>Bank of Utah Championship</t>
+          <t>Butterfield Bermuda Championship</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
@@ -4166,654 +4166,39 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Jackson Suber</t>
+          <t>Kevin Yu</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>0.163</v>
+        <v>0.4867</v>
       </c>
       <c r="C92" t="n">
-        <v>0.823</v>
+        <v>0.4171</v>
       </c>
       <c r="D92" t="n">
-        <v>0.418</v>
+        <v>0.4867</v>
       </c>
       <c r="E92" t="n">
-        <v>-0.05</v>
+        <v>0.1667</v>
       </c>
       <c r="F92" t="n">
-        <v>0.075</v>
+        <v>0.1</v>
       </c>
       <c r="G92" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="H92" t="n">
+        <v>0.896</v>
+      </c>
+      <c r="I92" t="n">
         <v>-0.01</v>
       </c>
-      <c r="H92" t="n">
-        <v>0.61</v>
-      </c>
-      <c r="I92" t="n">
-        <v>0.02</v>
-      </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>Bank of Utah Championship</t>
+          <t>Butterfield Bermuda Championship</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
-        <is>
-          <t>PGA Tour</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>Adam Svensson</t>
-        </is>
-      </c>
-      <c r="B93" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="C93" t="n">
-        <v>0.823</v>
-      </c>
-      <c r="D93" t="n">
-        <v>-0.098</v>
-      </c>
-      <c r="E93" t="n">
-        <v>-0.211</v>
-      </c>
-      <c r="F93" t="n">
-        <v>0.027</v>
-      </c>
-      <c r="G93" t="n">
-        <v>0</v>
-      </c>
-      <c r="H93" t="n">
-        <v>-0.78</v>
-      </c>
-      <c r="I93" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="J93" t="inlineStr">
-        <is>
-          <t>Bank of Utah Championship</t>
-        </is>
-      </c>
-      <c r="K93" t="inlineStr">
-        <is>
-          <t>PGA Tour</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>Jesper Svensson</t>
-        </is>
-      </c>
-      <c r="B94" t="n">
-        <v>0.221</v>
-      </c>
-      <c r="C94" t="n">
-        <v>0.823</v>
-      </c>
-      <c r="D94" t="n">
-        <v>-0.3</v>
-      </c>
-      <c r="E94" t="n">
-        <v>-0.244</v>
-      </c>
-      <c r="F94" t="n">
-        <v>-0.094</v>
-      </c>
-      <c r="G94" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="H94" t="n">
-        <v>-0.42</v>
-      </c>
-      <c r="I94" t="n">
-        <v>0</v>
-      </c>
-      <c r="J94" t="inlineStr">
-        <is>
-          <t>Bank of Utah Championship</t>
-        </is>
-      </c>
-      <c r="K94" t="inlineStr">
-        <is>
-          <t>PGA Tour</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>Nick Taylor</t>
-        </is>
-      </c>
-      <c r="B95" t="n">
-        <v>-0.2137</v>
-      </c>
-      <c r="C95" t="n">
-        <v>0.115</v>
-      </c>
-      <c r="D95" t="n">
-        <v>-0.275</v>
-      </c>
-      <c r="E95" t="n">
-        <v>0.5024999999999999</v>
-      </c>
-      <c r="F95" t="n">
-        <v>0.0138</v>
-      </c>
-      <c r="G95" t="n">
-        <v>-0.04</v>
-      </c>
-      <c r="H95" t="n">
-        <v>-0.0825</v>
-      </c>
-      <c r="I95" t="n">
-        <v>-0.04</v>
-      </c>
-      <c r="J95" t="inlineStr">
-        <is>
-          <t>Bank of Utah Championship</t>
-        </is>
-      </c>
-      <c r="K95" t="inlineStr">
-        <is>
-          <t>PGA Tour</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>Davis Thompson</t>
-        </is>
-      </c>
-      <c r="B96" t="n">
-        <v>0.236</v>
-      </c>
-      <c r="C96" t="n">
-        <v>0.823</v>
-      </c>
-      <c r="D96" t="n">
-        <v>0.524</v>
-      </c>
-      <c r="E96" t="n">
-        <v>-0.093</v>
-      </c>
-      <c r="F96" t="n">
-        <v>-0.06900000000000001</v>
-      </c>
-      <c r="G96" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="H96" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="I96" t="n">
-        <v>-0.06</v>
-      </c>
-      <c r="J96" t="inlineStr">
-        <is>
-          <t>Bank of Utah Championship</t>
-        </is>
-      </c>
-      <c r="K96" t="inlineStr">
-        <is>
-          <t>PGA Tour</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>Alejandro Tosti</t>
-        </is>
-      </c>
-      <c r="B97" t="n">
-        <v>0.034</v>
-      </c>
-      <c r="C97" t="n">
-        <v>0.823</v>
-      </c>
-      <c r="D97" t="n">
-        <v>-0.602</v>
-      </c>
-      <c r="E97" t="n">
-        <v>-0.52</v>
-      </c>
-      <c r="F97" t="n">
-        <v>-0.097</v>
-      </c>
-      <c r="G97" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="H97" t="n">
-        <v>-1.19</v>
-      </c>
-      <c r="I97" t="n">
-        <v>-0</v>
-      </c>
-      <c r="J97" t="inlineStr">
-        <is>
-          <t>Bank of Utah Championship</t>
-        </is>
-      </c>
-      <c r="K97" t="inlineStr">
-        <is>
-          <t>PGA Tour</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>Erik Van Rooyen</t>
-        </is>
-      </c>
-      <c r="B98" t="n">
-        <v>-0.203</v>
-      </c>
-      <c r="C98" t="n">
-        <v>0.823</v>
-      </c>
-      <c r="D98" t="n">
-        <v>-0.458</v>
-      </c>
-      <c r="E98" t="n">
-        <v>0.135</v>
-      </c>
-      <c r="F98" t="n">
-        <v>0.004</v>
-      </c>
-      <c r="G98" t="n">
-        <v>-0.05</v>
-      </c>
-      <c r="H98" t="n">
-        <v>-0.52</v>
-      </c>
-      <c r="I98" t="n">
-        <v>-0.02</v>
-      </c>
-      <c r="J98" t="inlineStr">
-        <is>
-          <t>Bank of Utah Championship</t>
-        </is>
-      </c>
-      <c r="K98" t="inlineStr">
-        <is>
-          <t>PGA Tour</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>John VanDerLaan</t>
-        </is>
-      </c>
-      <c r="B99" t="n">
-        <v>0.091</v>
-      </c>
-      <c r="C99" t="n">
-        <v>0.823</v>
-      </c>
-      <c r="D99" t="n">
-        <v>-0.363</v>
-      </c>
-      <c r="E99" t="n">
-        <v>-0.122</v>
-      </c>
-      <c r="F99" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="G99" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="H99" t="n">
-        <v>-0.39</v>
-      </c>
-      <c r="I99" t="n">
-        <v>-0.04</v>
-      </c>
-      <c r="J99" t="inlineStr">
-        <is>
-          <t>Bank of Utah Championship</t>
-        </is>
-      </c>
-      <c r="K99" t="inlineStr">
-        <is>
-          <t>PGA Tour</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>Kristoffer Ventura</t>
-        </is>
-      </c>
-      <c r="B100" t="n">
-        <v>0.461</v>
-      </c>
-      <c r="C100" t="n">
-        <v>0.823</v>
-      </c>
-      <c r="D100" t="n">
-        <v>0.038</v>
-      </c>
-      <c r="E100" t="n">
-        <v>-0.044</v>
-      </c>
-      <c r="F100" t="n">
-        <v>-0.131</v>
-      </c>
-      <c r="G100" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="H100" t="n">
-        <v>0.32</v>
-      </c>
-      <c r="I100" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="J100" t="inlineStr">
-        <is>
-          <t>Bank of Utah Championship</t>
-        </is>
-      </c>
-      <c r="K100" t="inlineStr">
-        <is>
-          <t>PGA Tour</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>Danny Walker</t>
-        </is>
-      </c>
-      <c r="B101" t="n">
-        <v>-0.25</v>
-      </c>
-      <c r="C101" t="n">
-        <v>0.823</v>
-      </c>
-      <c r="D101" t="n">
-        <v>-0.299</v>
-      </c>
-      <c r="E101" t="n">
-        <v>-0.28</v>
-      </c>
-      <c r="F101" t="n">
-        <v>-0.1</v>
-      </c>
-      <c r="G101" t="n">
-        <v>-0.04</v>
-      </c>
-      <c r="H101" t="n">
-        <v>-0.93</v>
-      </c>
-      <c r="I101" t="n">
-        <v>-0.03</v>
-      </c>
-      <c r="J101" t="inlineStr">
-        <is>
-          <t>Bank of Utah Championship</t>
-        </is>
-      </c>
-      <c r="K101" t="inlineStr">
-        <is>
-          <t>PGA Tour</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>Matt Wallace</t>
-        </is>
-      </c>
-      <c r="B102" t="n">
-        <v>0.116</v>
-      </c>
-      <c r="C102" t="n">
-        <v>0.823</v>
-      </c>
-      <c r="D102" t="n">
-        <v>0.5639999999999999</v>
-      </c>
-      <c r="E102" t="n">
-        <v>0.064</v>
-      </c>
-      <c r="F102" t="n">
-        <v>0.264</v>
-      </c>
-      <c r="G102" t="n">
-        <v>-0.02</v>
-      </c>
-      <c r="H102" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="I102" t="n">
-        <v>-0.05</v>
-      </c>
-      <c r="J102" t="inlineStr">
-        <is>
-          <t>Bank of Utah Championship</t>
-        </is>
-      </c>
-      <c r="K102" t="inlineStr">
-        <is>
-          <t>PGA Tour</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>Vince Whaley</t>
-        </is>
-      </c>
-      <c r="B103" t="n">
-        <v>-0.721</v>
-      </c>
-      <c r="C103" t="n">
-        <v>0.823</v>
-      </c>
-      <c r="D103" t="n">
-        <v>-0.54</v>
-      </c>
-      <c r="E103" t="n">
-        <v>0.402</v>
-      </c>
-      <c r="F103" t="n">
-        <v>0.164</v>
-      </c>
-      <c r="G103" t="n">
-        <v>-0.15</v>
-      </c>
-      <c r="H103" t="n">
-        <v>-0.7</v>
-      </c>
-      <c r="I103" t="n">
-        <v>-0.02</v>
-      </c>
-      <c r="J103" t="inlineStr">
-        <is>
-          <t>Bank of Utah Championship</t>
-        </is>
-      </c>
-      <c r="K103" t="inlineStr">
-        <is>
-          <t>PGA Tour</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>Aaron Wise</t>
-        </is>
-      </c>
-      <c r="B104" t="n">
-        <v>-0.389</v>
-      </c>
-      <c r="C104" t="n">
-        <v>0.823</v>
-      </c>
-      <c r="D104" t="n">
-        <v>-0.317</v>
-      </c>
-      <c r="E104" t="n">
-        <v>-0.184</v>
-      </c>
-      <c r="F104" t="n">
-        <v>0.083</v>
-      </c>
-      <c r="G104" t="n">
-        <v>-0.03</v>
-      </c>
-      <c r="H104" t="n">
-        <v>-0.8100000000000001</v>
-      </c>
-      <c r="I104" t="n">
-        <v>-0.04</v>
-      </c>
-      <c r="J104" t="inlineStr">
-        <is>
-          <t>Bank of Utah Championship</t>
-        </is>
-      </c>
-      <c r="K104" t="inlineStr">
-        <is>
-          <t>PGA Tour</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>Dylan Wu</t>
-        </is>
-      </c>
-      <c r="B105" t="n">
-        <v>-0.437</v>
-      </c>
-      <c r="C105" t="n">
-        <v>0.823</v>
-      </c>
-      <c r="D105" t="n">
-        <v>-0.186</v>
-      </c>
-      <c r="E105" t="n">
-        <v>-0.083</v>
-      </c>
-      <c r="F105" t="n">
-        <v>-0.023</v>
-      </c>
-      <c r="G105" t="n">
-        <v>-0.01</v>
-      </c>
-      <c r="H105" t="n">
-        <v>-0.73</v>
-      </c>
-      <c r="I105" t="n">
-        <v>-0.05</v>
-      </c>
-      <c r="J105" t="inlineStr">
-        <is>
-          <t>Bank of Utah Championship</t>
-        </is>
-      </c>
-      <c r="K105" t="inlineStr">
-        <is>
-          <t>PGA Tour</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>Sudarshan Yellamaraju</t>
-        </is>
-      </c>
-      <c r="B106" t="n">
-        <v>0.115</v>
-      </c>
-      <c r="C106" t="n">
-        <v>0.823</v>
-      </c>
-      <c r="D106" t="n">
-        <v>0.016</v>
-      </c>
-      <c r="E106" t="n">
-        <v>-0.06900000000000001</v>
-      </c>
-      <c r="F106" t="n">
-        <v>-0.015</v>
-      </c>
-      <c r="G106" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="H106" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="I106" t="n">
-        <v>-0.04</v>
-      </c>
-      <c r="J106" t="inlineStr">
-        <is>
-          <t>Bank of Utah Championship</t>
-        </is>
-      </c>
-      <c r="K106" t="inlineStr">
-        <is>
-          <t>PGA Tour</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>Kevin Yu</t>
-        </is>
-      </c>
-      <c r="B107" t="n">
-        <v>0.279</v>
-      </c>
-      <c r="C107" t="n">
-        <v>0.823</v>
-      </c>
-      <c r="D107" t="n">
-        <v>0.188</v>
-      </c>
-      <c r="E107" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="F107" t="n">
-        <v>0.068</v>
-      </c>
-      <c r="G107" t="n">
-        <v>-0</v>
-      </c>
-      <c r="H107" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="I107" t="n">
-        <v>-0.01</v>
-      </c>
-      <c r="J107" t="inlineStr">
-        <is>
-          <t>Bank of Utah Championship</t>
-        </is>
-      </c>
-      <c r="K107" t="inlineStr">
         <is>
           <t>PGA Tour</t>
         </is>

--- a/datagolf/workbooks/StatCaddy_Field_latest.xlsx
+++ b/datagolf/workbooks/StatCaddy_Field_latest.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K92"/>
+  <dimension ref="A1:K104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,36 +476,36 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Zac Blair</t>
+          <t>Zach Bauchou</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-0.335</v>
+        <v>0.1367</v>
       </c>
       <c r="C2" t="n">
-        <v>0.323</v>
+        <v>0.3229</v>
       </c>
       <c r="D2" t="n">
-        <v>0.329</v>
+        <v>0.2833</v>
       </c>
       <c r="E2" t="n">
-        <v>0.115</v>
+        <v>0.3083</v>
       </c>
       <c r="F2" t="n">
-        <v>0.08</v>
+        <v>-0.095</v>
       </c>
       <c r="G2" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>0.19</v>
+        <v>1.05</v>
       </c>
       <c r="I2" t="n">
-        <v>0.02</v>
+        <v>-0.04</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Butterfield Bermuda Championship</t>
+          <t>VidantaWorld Mexico Open</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -517,36 +517,36 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Chandler Blanchet</t>
+          <t>Christiaan Bezuidenhout</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.048</v>
+        <v>-0.2983</v>
       </c>
       <c r="C3" t="n">
-        <v>0.323</v>
+        <v>0.2971</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.1</v>
+        <v>0.5417</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.244</v>
+        <v>0.195</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.326</v>
+        <v>0.1017</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.04</v>
+        <v>-0.02</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.62</v>
+        <v>0.64</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.04</v>
+        <v>0</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Butterfield Bermuda Championship</t>
+          <t>VidantaWorld Mexico Open</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -558,36 +558,36 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Rafael Campos</t>
+          <t>Zac Blair</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-0.151</v>
+        <v>-0.332</v>
       </c>
       <c r="C4" t="n">
         <v>0.323</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.376</v>
+        <v>0.262</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.397</v>
+        <v>0.155</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.293</v>
+        <v>0.074</v>
       </c>
       <c r="G4" t="n">
-        <v>0.09</v>
+        <v>-0.16</v>
       </c>
       <c r="H4" t="n">
-        <v>-1.22</v>
+        <v>0.16</v>
       </c>
       <c r="I4" t="n">
-        <v>0.12</v>
+        <v>-0.04</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Butterfield Bermuda Championship</t>
+          <t>VidantaWorld Mexico Open</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -599,36 +599,36 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Cameron Champ</t>
+          <t>Chandler Blanchet</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.306</v>
+        <v>0.066</v>
       </c>
       <c r="C5" t="n">
         <v>0.323</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.726</v>
+        <v>-0.038</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.285</v>
+        <v>-0.168</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.315</v>
+        <v>-0.314</v>
       </c>
       <c r="G5" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="H5" t="n">
+        <v>-0.45</v>
+      </c>
+      <c r="I5" t="n">
         <v>-0.04</v>
       </c>
-      <c r="H5" t="n">
-        <v>-1.02</v>
-      </c>
-      <c r="I5" t="n">
-        <v>-0.06</v>
-      </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Butterfield Bermuda Championship</t>
+          <t>VidantaWorld Mexico Open</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -640,36 +640,36 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Davis Chatfield</t>
+          <t>Blades Brown</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-0.469</v>
+        <v>0.374</v>
       </c>
       <c r="C6" t="n">
         <v>0.323</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.067</v>
+        <v>0.272</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.1</v>
+        <v>0.064</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.055</v>
+        <v>-0.054</v>
       </c>
       <c r="G6" t="n">
-        <v>0.02</v>
+        <v>0.04</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.6899999999999999</v>
+        <v>0.66</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.04</v>
+        <v>0.01</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Butterfield Bermuda Championship</t>
+          <t>VidantaWorld Mexico Open</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -681,36 +681,36 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Luke Clanton</t>
+          <t>Brian Campbell</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-0.184</v>
+        <v>-0.523</v>
       </c>
       <c r="C7" t="n">
         <v>0.323</v>
       </c>
       <c r="D7" t="n">
-        <v>0.378</v>
+        <v>-0.155</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.07099999999999999</v>
+        <v>-0.112</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.095</v>
+        <v>-0.061</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>-0.16</v>
       </c>
       <c r="H7" t="n">
-        <v>0.03</v>
+        <v>-0.85</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.05</v>
+        <v>0.04</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Butterfield Bermuda Championship</t>
+          <t>VidantaWorld Mexico Open</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -722,36 +722,36 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Eric Cole</t>
+          <t>Rafael Campos</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-0.318</v>
+        <v>-0.126</v>
       </c>
       <c r="C8" t="n">
         <v>0.323</v>
       </c>
       <c r="D8" t="n">
-        <v>0.254</v>
+        <v>-0.352</v>
       </c>
       <c r="E8" t="n">
-        <v>0.282</v>
+        <v>-0.363</v>
       </c>
       <c r="F8" t="n">
-        <v>0.241</v>
+        <v>-0.256</v>
       </c>
       <c r="G8" t="n">
-        <v>0.06</v>
+        <v>0.04</v>
       </c>
       <c r="H8" t="n">
-        <v>0.46</v>
+        <v>-1.1</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.04</v>
+        <v>0.04</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Butterfield Bermuda Championship</t>
+          <t>VidantaWorld Mexico Open</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -763,36 +763,36 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Corey Conners</t>
+          <t>Davis Chatfield</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.384</v>
+        <v>-0.456</v>
       </c>
       <c r="C9" t="n">
         <v>0.323</v>
       </c>
       <c r="D9" t="n">
-        <v>0.536</v>
+        <v>-0.074</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.094</v>
+        <v>-0.07199999999999999</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.016</v>
+        <v>-0.07099999999999999</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.14</v>
+        <v>-0.17</v>
       </c>
       <c r="H9" t="n">
-        <v>0.8100000000000001</v>
+        <v>-0.67</v>
       </c>
       <c r="I9" t="n">
         <v>-0.04</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Butterfield Bermuda Championship</t>
+          <t>VidantaWorld Mexico Open</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -804,36 +804,36 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Trace Crowe</t>
+          <t>Luke Clanton</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.074</v>
+        <v>-0.138</v>
       </c>
       <c r="C10" t="n">
         <v>0.323</v>
       </c>
       <c r="D10" t="n">
-        <v>0.358</v>
+        <v>0.363</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.022</v>
+        <v>-0.003</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.043</v>
+        <v>-0.096</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.01</v>
+        <v>-0</v>
       </c>
       <c r="H10" t="n">
-        <v>0.37</v>
+        <v>0.12</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.01</v>
+        <v>-0.04</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Butterfield Bermuda Championship</t>
+          <t>VidantaWorld Mexico Open</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -845,36 +845,36 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Joel Dahmen</t>
+          <t>Wyndham Clark</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.195</v>
+        <v>0.185</v>
       </c>
       <c r="C11" t="n">
-        <v>0.323</v>
+        <v>3.6867</v>
       </c>
       <c r="D11" t="n">
-        <v>0.141</v>
+        <v>0.2512</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.498</v>
+        <v>0.57</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.178</v>
+        <v>0.4387</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.09</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.34</v>
+        <v>0.106</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.05</v>
+        <v>-0.03</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Butterfield Bermuda Championship</t>
+          <t>VidantaWorld Mexico Open</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -886,36 +886,36 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Cam Davis</t>
+          <t>Corey Conners</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>-0.605</v>
+        <v>0.444</v>
       </c>
       <c r="C12" t="n">
         <v>0.323</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.362</v>
+        <v>0.633</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.169</v>
+        <v>-0.096</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.116</v>
+        <v>-0.018</v>
       </c>
       <c r="G12" t="n">
-        <v>0.15</v>
+        <v>-0.02</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.25</v>
+        <v>0.96</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.05</v>
+        <v>-0.04</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Butterfield Bermuda Championship</t>
+          <t>VidantaWorld Mexico Open</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -927,36 +927,36 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Zecheng Dou</t>
+          <t>Pierceson Coody</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.118</v>
+        <v>-0.06</v>
       </c>
       <c r="C13" t="n">
-        <v>0.323</v>
+        <v>0.2156</v>
       </c>
       <c r="D13" t="n">
-        <v>0.189</v>
+        <v>-0.5763</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.167</v>
+        <v>-0.1562</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.068</v>
+        <v>0.0275</v>
       </c>
       <c r="G13" t="n">
-        <v>-0</v>
+        <v>0.01</v>
       </c>
       <c r="H13" t="n">
-        <v>0.07000000000000001</v>
+        <v>-1.195</v>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>-0.04</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Butterfield Bermuda Championship</t>
+          <t>VidantaWorld Mexico Open</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -968,36 +968,36 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Adrien Dumont De Chassart</t>
+          <t>Trace Crowe</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>-0.663</v>
+        <v>0.025</v>
       </c>
       <c r="C14" t="n">
         <v>0.323</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.155</v>
+        <v>0.291</v>
       </c>
       <c r="E14" t="n">
-        <v>0.305</v>
+        <v>0.042</v>
       </c>
       <c r="F14" t="n">
-        <v>0.215</v>
+        <v>-0.067</v>
       </c>
       <c r="G14" t="n">
-        <v>0.14</v>
+        <v>0.03</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.3</v>
+        <v>0.29</v>
       </c>
       <c r="I14" t="n">
-        <v>0.03</v>
+        <v>-0.03</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Butterfield Bermuda Championship</t>
+          <t>VidantaWorld Mexico Open</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1009,36 +1009,36 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Nick Dunlap</t>
+          <t>Joel Dahmen</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>-1.168</v>
+        <v>0.232</v>
       </c>
       <c r="C15" t="n">
         <v>0.323</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.189</v>
+        <v>0.156</v>
       </c>
       <c r="E15" t="n">
-        <v>0.068</v>
+        <v>-0.483</v>
       </c>
       <c r="F15" t="n">
-        <v>0.135</v>
+        <v>-0.211</v>
       </c>
       <c r="G15" t="n">
-        <v>0.24</v>
+        <v>-0.08</v>
       </c>
       <c r="H15" t="n">
-        <v>-1.15</v>
+        <v>-0.3</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.05</v>
+        <v>0.02</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Butterfield Bermuda Championship</t>
+          <t>VidantaWorld Mexico Open</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1050,36 +1050,36 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Austin Eckroat</t>
+          <t>Cam Davis</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-0.045</v>
+        <v>-0.466</v>
       </c>
       <c r="C16" t="n">
         <v>0.323</v>
       </c>
       <c r="D16" t="n">
-        <v>0.206</v>
+        <v>-0.265</v>
       </c>
       <c r="E16" t="n">
-        <v>0.118</v>
+        <v>-0.098</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.11</v>
+        <v>-0.08799999999999999</v>
       </c>
       <c r="G16" t="n">
-        <v>0.01</v>
+        <v>0.03</v>
       </c>
       <c r="H16" t="n">
-        <v>0.17</v>
+        <v>-0.92</v>
       </c>
       <c r="I16" t="n">
-        <v>-0</v>
+        <v>-0.04</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Butterfield Bermuda Championship</t>
+          <t>VidantaWorld Mexico Open</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1091,36 +1091,36 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A.J. Ewart</t>
+          <t>Zecheng Dou</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>-0.315</v>
+        <v>0.054</v>
       </c>
       <c r="C17" t="n">
         <v>0.323</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.08500000000000001</v>
+        <v>0.223</v>
       </c>
       <c r="E17" t="n">
-        <v>0.367</v>
+        <v>-0.197</v>
       </c>
       <c r="F17" t="n">
-        <v>0.053</v>
+        <v>-0.026</v>
       </c>
       <c r="G17" t="n">
-        <v>0.08</v>
+        <v>0.05</v>
       </c>
       <c r="H17" t="n">
-        <v>0.02</v>
+        <v>0.05</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.04</v>
+        <v>-0</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Butterfield Bermuda Championship</t>
+          <t>VidantaWorld Mexico Open</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1132,11 +1132,11 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Patrick Fishburn</t>
+          <t>Adrien Dumont De Chassart</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.148</v>
+        <v>-0.595</v>
       </c>
       <c r="C18" t="n">
         <v>0.323</v>
@@ -1145,23 +1145,23 @@
         <v>-0.139</v>
       </c>
       <c r="E18" t="n">
-        <v>0.112</v>
+        <v>0.362</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.06900000000000001</v>
+        <v>0.209</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.01</v>
+        <v>0.04</v>
       </c>
       <c r="H18" t="n">
-        <v>0.05</v>
+        <v>-0.16</v>
       </c>
       <c r="I18" t="n">
-        <v>0.01</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Butterfield Bermuda Championship</t>
+          <t>VidantaWorld Mexico Open</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1173,36 +1173,36 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>David Ford</t>
+          <t>Nick Dunlap</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.494</v>
+        <v>-1.131</v>
       </c>
       <c r="C19" t="n">
         <v>0.323</v>
       </c>
       <c r="D19" t="n">
-        <v>0.07000000000000001</v>
+        <v>-0.205</v>
       </c>
       <c r="E19" t="n">
-        <v>0.035</v>
+        <v>0.115</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.17</v>
+        <v>0.156</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.12</v>
+        <v>-0.02</v>
       </c>
       <c r="H19" t="n">
-        <v>0.43</v>
+        <v>-1.06</v>
       </c>
       <c r="I19" t="n">
         <v>-0.04</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Butterfield Bermuda Championship</t>
+          <t>VidantaWorld Mexico Open</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -1214,36 +1214,36 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Dylan Frittelli</t>
+          <t>Austin Eckroat</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>-0.588</v>
+        <v>-0.05</v>
       </c>
       <c r="C20" t="n">
         <v>0.323</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.677</v>
+        <v>0.202</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.16</v>
+        <v>0.123</v>
       </c>
       <c r="F20" t="n">
-        <v>0.047</v>
+        <v>-0.113</v>
       </c>
       <c r="G20" t="n">
-        <v>0.2</v>
+        <v>-0</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.38</v>
+        <v>0.16</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.01</v>
+        <v>0.01</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Butterfield Bermuda Championship</t>
+          <t>VidantaWorld Mexico Open</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -1255,36 +1255,36 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Brice Garnett</t>
+          <t>A.J. Ewart</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>-0.16</v>
+        <v>-0.293</v>
       </c>
       <c r="C21" t="n">
         <v>0.323</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.343</v>
+        <v>-0.109</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.07099999999999999</v>
+        <v>0.412</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.008999999999999999</v>
+        <v>0.028</v>
       </c>
       <c r="G21" t="n">
         <v>-0.01</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.58</v>
+        <v>0.04</v>
       </c>
       <c r="I21" t="n">
-        <v>0.03</v>
+        <v>-0.04</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Butterfield Bermuda Championship</t>
+          <t>VidantaWorld Mexico Open</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -1296,36 +1296,36 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Lucas Glover</t>
+          <t>Tony Finau</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>-0.066</v>
+        <v>0.095</v>
       </c>
       <c r="C22" t="n">
-        <v>0.323</v>
+        <v>0.0586</v>
       </c>
       <c r="D22" t="n">
-        <v>0.235</v>
+        <v>-0.2767</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.636</v>
+        <v>-0.6967</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.091</v>
+        <v>0.3767</v>
       </c>
       <c r="G22" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="H22" t="n">
+        <v>-1.0033</v>
+      </c>
+      <c r="I22" t="n">
         <v>-0.04</v>
       </c>
-      <c r="H22" t="n">
-        <v>-0.5600000000000001</v>
-      </c>
-      <c r="I22" t="n">
-        <v>-0.02</v>
-      </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Butterfield Bermuda Championship</t>
+          <t>VidantaWorld Mexico Open</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -1337,36 +1337,36 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Will Gordon</t>
+          <t>Patrick Fishburn</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-0.117</v>
+        <v>0.08</v>
       </c>
       <c r="C23" t="n">
         <v>0.323</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.366</v>
+        <v>-0.077</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.273</v>
+        <v>0.06</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.235</v>
+        <v>-0.077</v>
       </c>
       <c r="G23" t="n">
         <v>0.03</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.99</v>
+        <v>-0.01</v>
       </c>
       <c r="I23" t="n">
-        <v>0.09</v>
+        <v>-0.04</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Butterfield Bermuda Championship</t>
+          <t>VidantaWorld Mexico Open</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -1378,36 +1378,36 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Max Greyserman</t>
+          <t>Steven Fisk</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.3429</v>
+        <v>0.288</v>
       </c>
       <c r="C24" t="n">
-        <v>0.17</v>
+        <v>0.0733</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.6943</v>
+        <v>-0.678</v>
       </c>
       <c r="E24" t="n">
-        <v>0.6657</v>
+        <v>-0.756</v>
       </c>
       <c r="F24" t="n">
+        <v>-0.024</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="H24" t="n">
+        <v>-0.835</v>
+      </c>
+      <c r="I24" t="n">
         <v>-0.04</v>
       </c>
-      <c r="G24" t="n">
-        <v>-0.02</v>
-      </c>
-      <c r="H24" t="n">
-        <v>-0.018</v>
-      </c>
-      <c r="I24" t="n">
-        <v>0.04</v>
-      </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Butterfield Bermuda Championship</t>
+          <t>VidantaWorld Mexico Open</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -1419,36 +1419,36 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Emiliano Grillo</t>
+          <t>David Ford</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.026</v>
+        <v>0.552</v>
       </c>
       <c r="C25" t="n">
         <v>0.323</v>
       </c>
       <c r="D25" t="n">
-        <v>0.239</v>
+        <v>0.112</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.122</v>
+        <v>-0.017</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.19</v>
+        <v>-0.176</v>
       </c>
       <c r="G25" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.05</v>
+        <v>0.47</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.02</v>
+        <v>-0.04</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Butterfield Bermuda Championship</t>
+          <t>VidantaWorld Mexico Open</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -1460,36 +1460,36 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Adam Hadwin</t>
+          <t>Brice Garnett</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-0.217</v>
+        <v>-0.111</v>
       </c>
       <c r="C26" t="n">
         <v>0.323</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.283</v>
+        <v>-0.296</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.053</v>
+        <v>-0.063</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.135</v>
+        <v>0.041</v>
       </c>
       <c r="G26" t="n">
-        <v>0.08</v>
+        <v>-0.09</v>
       </c>
       <c r="H26" t="n">
-        <v>-0.6899999999999999</v>
+        <v>-0.43</v>
       </c>
       <c r="I26" t="n">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Butterfield Bermuda Championship</t>
+          <t>VidantaWorld Mexico Open</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -1501,36 +1501,36 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Nick Hardy</t>
+          <t>Doug Ghim</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-0.008</v>
+        <v>0.55</v>
       </c>
       <c r="C27" t="n">
-        <v>0.323</v>
+        <v>0.6283</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.4</v>
+        <v>0.198</v>
       </c>
       <c r="E27" t="n">
-        <v>-0.193</v>
+        <v>0.236</v>
       </c>
       <c r="F27" t="n">
-        <v>-0.172</v>
+        <v>0.166</v>
       </c>
       <c r="G27" t="n">
-        <v>0.06</v>
+        <v>0.03</v>
       </c>
       <c r="H27" t="n">
-        <v>-0.77</v>
+        <v>1.06</v>
       </c>
       <c r="I27" t="n">
-        <v>0</v>
+        <v>-0.04</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Butterfield Bermuda Championship</t>
+          <t>VidantaWorld Mexico Open</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -1542,36 +1542,36 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Harry Higgs</t>
+          <t>Will Gordon</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.222</v>
+        <v>-0.138</v>
       </c>
       <c r="C28" t="n">
         <v>0.323</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.343</v>
+        <v>-0.335</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.152</v>
+        <v>-0.305</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.104</v>
+        <v>-0.243</v>
       </c>
       <c r="G28" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="H28" t="n">
-        <v>-0.82</v>
+        <v>-1.02</v>
       </c>
       <c r="I28" t="n">
-        <v>0.05</v>
+        <v>-0.01</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>Butterfield Bermuda Championship</t>
+          <t>VidantaWorld Mexico Open</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -1583,36 +1583,36 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Kensei Hirata</t>
+          <t>Max Greyserman</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.345</v>
+        <v>0.3429</v>
       </c>
       <c r="C29" t="n">
-        <v>0.323</v>
+        <v>0.17</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.669</v>
+        <v>-0.6943</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.214</v>
+        <v>0.6657</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.089</v>
+        <v>-0.04</v>
       </c>
       <c r="G29" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="H29" t="n">
+        <v>-0.018</v>
+      </c>
+      <c r="I29" t="n">
         <v>0.04</v>
       </c>
-      <c r="H29" t="n">
-        <v>-1.32</v>
-      </c>
-      <c r="I29" t="n">
-        <v>-0.04</v>
-      </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>Butterfield Bermuda Championship</t>
+          <t>VidantaWorld Mexico Open</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -1624,36 +1624,36 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Lee Hodges</t>
+          <t>Ben Griffin</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.3175</v>
+        <v>0.182</v>
       </c>
       <c r="C30" t="n">
-        <v>0.15</v>
+        <v>0.323</v>
       </c>
       <c r="D30" t="n">
-        <v>0.0775</v>
+        <v>0.533</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.145</v>
+        <v>0.185</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.12</v>
+        <v>0.278</v>
       </c>
       <c r="G30" t="n">
-        <v>0.02</v>
+        <v>-0.01</v>
       </c>
       <c r="H30" t="n">
-        <v>0.1</v>
+        <v>1.18</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.02</v>
+        <v>0.03</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>Butterfield Bermuda Championship</t>
+          <t>VidantaWorld Mexico Open</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -1665,36 +1665,36 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Rico Hoey</t>
+          <t>Emiliano Grillo</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.513</v>
+        <v>0.02</v>
       </c>
       <c r="C31" t="n">
         <v>0.323</v>
       </c>
       <c r="D31" t="n">
-        <v>0.288</v>
+        <v>0.234</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.201</v>
+        <v>-0.158</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.036</v>
+        <v>-0.162</v>
       </c>
       <c r="G31" t="n">
-        <v>-0.1</v>
+        <v>-0.06</v>
       </c>
       <c r="H31" t="n">
-        <v>0.5600000000000001</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="I31" t="n">
-        <v>0.02</v>
+        <v>0.08</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>Butterfield Bermuda Championship</t>
+          <t>VidantaWorld Mexico Open</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -1706,36 +1706,36 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Charley Hoffman</t>
+          <t>Harry Hall</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.132</v>
+        <v>-0.007</v>
       </c>
       <c r="C32" t="n">
         <v>0.323</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.443</v>
+        <v>0.276</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.472</v>
+        <v>0.293</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.189</v>
+        <v>0.275</v>
       </c>
       <c r="G32" t="n">
-        <v>0.08</v>
+        <v>-0.02</v>
       </c>
       <c r="H32" t="n">
-        <v>-1.24</v>
+        <v>0.84</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.03</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Butterfield Bermuda Championship</t>
+          <t>VidantaWorld Mexico Open</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -1747,36 +1747,36 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Tom Hoge</t>
+          <t>Garrick Higgo</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.2</v>
+        <v>-0.258</v>
       </c>
       <c r="C33" t="n">
-        <v>0.1275</v>
+        <v>0.323</v>
       </c>
       <c r="D33" t="n">
-        <v>0.5029</v>
+        <v>-0.492</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.2643</v>
+        <v>0.163</v>
       </c>
       <c r="F33" t="n">
+        <v>-0.076</v>
+      </c>
+      <c r="G33" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H33" t="n">
+        <v>-0.66</v>
+      </c>
+      <c r="I33" t="n">
         <v>-0.03</v>
       </c>
-      <c r="G33" t="n">
-        <v>-0.02</v>
-      </c>
-      <c r="H33" t="n">
-        <v>-0.4025</v>
-      </c>
-      <c r="I33" t="n">
-        <v>-0.04</v>
-      </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Butterfield Bermuda Championship</t>
+          <t>VidantaWorld Mexico Open</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -1788,36 +1788,36 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Mark Hubbard</t>
+          <t>Harry Higgs</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.24</v>
+        <v>-0.263</v>
       </c>
       <c r="C34" t="n">
         <v>0.323</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.074</v>
+        <v>-0.413</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.185</v>
+        <v>-0.182</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.045</v>
+        <v>-0.123</v>
       </c>
       <c r="G34" t="n">
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.55</v>
+        <v>-0.98</v>
       </c>
       <c r="I34" t="n">
-        <v>0.08</v>
+        <v>-0.05</v>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Butterfield Bermuda Championship</t>
+          <t>VidantaWorld Mexico Open</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -1829,36 +1829,36 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Mackenzie Hughes</t>
+          <t>Joe Highsmith</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.174</v>
+        <v>-0.195</v>
       </c>
       <c r="C35" t="n">
         <v>0.323</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.275</v>
+        <v>-0.107</v>
       </c>
       <c r="E35" t="n">
-        <v>0.272</v>
+        <v>-0.205</v>
       </c>
       <c r="F35" t="n">
-        <v>0.312</v>
+        <v>-0.055</v>
       </c>
       <c r="G35" t="n">
-        <v>0.08</v>
+        <v>0.02</v>
       </c>
       <c r="H35" t="n">
-        <v>0.14</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.06</v>
+        <v>-0</v>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Butterfield Bermuda Championship</t>
+          <t>VidantaWorld Mexico Open</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -1870,36 +1870,36 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Ben James</t>
+          <t>Kensei Hirata</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.493</v>
+        <v>-0.35</v>
       </c>
       <c r="C36" t="n">
         <v>0.323</v>
       </c>
       <c r="D36" t="n">
-        <v>0.507</v>
+        <v>-0.591</v>
       </c>
       <c r="E36" t="n">
-        <v>0.135</v>
+        <v>-0.179</v>
       </c>
       <c r="F36" t="n">
-        <v>0.142</v>
+        <v>-0.112</v>
       </c>
       <c r="G36" t="n">
-        <v>-0.14</v>
+        <v>-0.08</v>
       </c>
       <c r="H36" t="n">
-        <v>1.28</v>
+        <v>-1.23</v>
       </c>
       <c r="I36" t="n">
         <v>-0.04</v>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Butterfield Bermuda Championship</t>
+          <t>VidantaWorld Mexico Open</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -1911,36 +1911,36 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Takumi Kanaya</t>
+          <t>Lee Hodges</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-0.0167</v>
+        <v>0.3175</v>
       </c>
       <c r="C37" t="n">
-        <v>0.1271</v>
+        <v>0.15</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.46</v>
+        <v>0.0775</v>
       </c>
       <c r="E37" t="n">
-        <v>0.08500000000000001</v>
+        <v>-0.145</v>
       </c>
       <c r="F37" t="n">
-        <v>0.3317</v>
+        <v>-0.12</v>
       </c>
       <c r="G37" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="H37" t="n">
-        <v>-0.112</v>
+        <v>0.1</v>
       </c>
       <c r="I37" t="n">
-        <v>0.02</v>
+        <v>-0.02</v>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Butterfield Bermuda Championship</t>
+          <t>VidantaWorld Mexico Open</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -1952,36 +1952,36 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Jeffrey Kang</t>
+          <t>Rico Hoey</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-0.163</v>
+        <v>0.433</v>
       </c>
       <c r="C38" t="n">
         <v>0.323</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.274</v>
+        <v>0.269</v>
       </c>
       <c r="E38" t="n">
-        <v>-0.339</v>
+        <v>-0.226</v>
       </c>
       <c r="F38" t="n">
-        <v>-0.006</v>
+        <v>-0</v>
       </c>
       <c r="G38" t="n">
-        <v>0.12</v>
+        <v>0.05</v>
       </c>
       <c r="H38" t="n">
-        <v>-0.78</v>
+        <v>0.48</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.04</v>
+        <v>-0.03</v>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>Butterfield Bermuda Championship</t>
+          <t>VidantaWorld Mexico Open</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -1993,36 +1993,36 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Chan Kim</t>
+          <t>Rasmus Hojgaard</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-0.059</v>
+        <v>-0.186</v>
       </c>
       <c r="C39" t="n">
         <v>0.323</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.078</v>
+        <v>-0.266</v>
       </c>
       <c r="E39" t="n">
-        <v>-0.267</v>
+        <v>0.409</v>
       </c>
       <c r="F39" t="n">
-        <v>0.018</v>
+        <v>-0.026</v>
       </c>
       <c r="G39" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="H39" t="n">
+        <v>-0.07000000000000001</v>
+      </c>
+      <c r="I39" t="n">
         <v>-0.03</v>
       </c>
-      <c r="H39" t="n">
-        <v>-0.39</v>
-      </c>
-      <c r="I39" t="n">
-        <v>0</v>
-      </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>Butterfield Bermuda Championship</t>
+          <t>VidantaWorld Mexico Open</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -2034,36 +2034,36 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Chris Kirk</t>
+          <t>Max Homa</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.144</v>
+        <v>0.1175</v>
       </c>
       <c r="C40" t="n">
-        <v>0.323</v>
+        <v>0.592</v>
       </c>
       <c r="D40" t="n">
-        <v>0.611</v>
+        <v>0.295</v>
       </c>
       <c r="E40" t="n">
-        <v>-0.268</v>
+        <v>0.38</v>
       </c>
       <c r="F40" t="n">
-        <v>0.109</v>
+        <v>0.1</v>
       </c>
       <c r="G40" t="n">
-        <v>-0.04</v>
+        <v>-0.01</v>
       </c>
       <c r="H40" t="n">
-        <v>0.6</v>
+        <v>0.7467</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.04</v>
+        <v>-0.02</v>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>Butterfield Bermuda Championship</t>
+          <t>VidantaWorld Mexico Open</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -2075,36 +2075,36 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Patton Kizzire</t>
+          <t>Billy Horschel</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-0.956</v>
+        <v>0.0214</v>
       </c>
       <c r="C41" t="n">
-        <v>0.323</v>
+        <v>0.2975</v>
       </c>
       <c r="D41" t="n">
-        <v>-0.214</v>
+        <v>0.7786</v>
       </c>
       <c r="E41" t="n">
-        <v>-0.093</v>
+        <v>0.1614</v>
       </c>
       <c r="F41" t="n">
-        <v>0.136</v>
+        <v>-0.3414</v>
       </c>
       <c r="G41" t="n">
-        <v>0.18</v>
+        <v>-0.01</v>
       </c>
       <c r="H41" t="n">
-        <v>-1.13</v>
+        <v>0.572</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.01</v>
+        <v>-0.03</v>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>Butterfield Bermuda Championship</t>
+          <t>VidantaWorld Mexico Open</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -2116,36 +2116,36 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Ben Kohles</t>
+          <t>Beau Hossler</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.3875</v>
+        <v>0.395</v>
       </c>
       <c r="C42" t="n">
-        <v>0.724</v>
+        <v>0.1971</v>
       </c>
       <c r="D42" t="n">
-        <v>0.495</v>
+        <v>0.0017</v>
       </c>
       <c r="E42" t="n">
-        <v>0.58</v>
+        <v>0.0833</v>
       </c>
       <c r="F42" t="n">
-        <v>0.0925</v>
+        <v>0.2367</v>
       </c>
       <c r="G42" t="n">
-        <v>0.03</v>
+        <v>-0.01</v>
       </c>
       <c r="H42" t="n">
-        <v>1.49</v>
+        <v>0.354</v>
       </c>
       <c r="I42" t="n">
-        <v>-0.04</v>
+        <v>-0.02</v>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>Butterfield Bermuda Championship</t>
+          <t>VidantaWorld Mexico Open</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -2157,36 +2157,36 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Christo Lamprecht</t>
+          <t>Mark Hubbard</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>-0.31</v>
+        <v>-0.24</v>
       </c>
       <c r="C43" t="n">
         <v>0.323</v>
       </c>
       <c r="D43" t="n">
-        <v>-1.169</v>
+        <v>-0.07199999999999999</v>
       </c>
       <c r="E43" t="n">
-        <v>-0.046</v>
+        <v>-0.17</v>
       </c>
       <c r="F43" t="n">
-        <v>-0.035</v>
+        <v>-0.006</v>
       </c>
       <c r="G43" t="n">
-        <v>0.16</v>
+        <v>-0.04</v>
       </c>
       <c r="H43" t="n">
-        <v>-1.56</v>
+        <v>-0.49</v>
       </c>
       <c r="I43" t="n">
-        <v>0.01</v>
+        <v>0.03</v>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>Butterfield Bermuda Championship</t>
+          <t>VidantaWorld Mexico Open</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -2198,36 +2198,36 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Hank Lebioda</t>
+          <t>Mackenzie Hughes</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>-0.304</v>
+        <v>-0.156</v>
       </c>
       <c r="C44" t="n">
         <v>0.323</v>
       </c>
       <c r="D44" t="n">
-        <v>-0.032</v>
+        <v>-0.205</v>
       </c>
       <c r="E44" t="n">
-        <v>-0.188</v>
+        <v>0.259</v>
       </c>
       <c r="F44" t="n">
-        <v>-0.055</v>
+        <v>0.323</v>
       </c>
       <c r="G44" t="n">
-        <v>0.09</v>
+        <v>0.01</v>
       </c>
       <c r="H44" t="n">
-        <v>-0.58</v>
+        <v>0.22</v>
       </c>
       <c r="I44" t="n">
-        <v>0.05</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>Butterfield Bermuda Championship</t>
+          <t>VidantaWorld Mexico Open</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -2239,36 +2239,36 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Haotong Li</t>
+          <t>Ben James</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.176</v>
+        <v>0.492</v>
       </c>
       <c r="C45" t="n">
         <v>0.323</v>
       </c>
       <c r="D45" t="n">
-        <v>0.035</v>
+        <v>0.445</v>
       </c>
       <c r="E45" t="n">
-        <v>-0.135</v>
+        <v>0.091</v>
       </c>
       <c r="F45" t="n">
-        <v>-0.235</v>
+        <v>0.104</v>
       </c>
       <c r="G45" t="n">
-        <v>0.01</v>
+        <v>-0.02</v>
       </c>
       <c r="H45" t="n">
-        <v>-0.16</v>
+        <v>1.13</v>
       </c>
       <c r="I45" t="n">
         <v>-0.04</v>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>Butterfield Bermuda Championship</t>
+          <t>VidantaWorld Mexico Open</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -2280,36 +2280,36 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Luke List</t>
+          <t>Takumi Kanaya</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>-0.042</v>
+        <v>-0.0167</v>
       </c>
       <c r="C46" t="n">
-        <v>0.323</v>
+        <v>0.1271</v>
       </c>
       <c r="D46" t="n">
-        <v>-0.5629999999999999</v>
+        <v>-0.46</v>
       </c>
       <c r="E46" t="n">
-        <v>-0.148</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="F46" t="n">
-        <v>-0.268</v>
+        <v>0.3317</v>
       </c>
       <c r="G46" t="n">
-        <v>0.07000000000000001</v>
+        <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>-1.02</v>
+        <v>-0.112</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.02</v>
+        <v>0.02</v>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>Butterfield Bermuda Championship</t>
+          <t>VidantaWorld Mexico Open</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -2321,36 +2321,36 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Justin Lower</t>
+          <t>Jeffrey Kang</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>-0.203</v>
+        <v>-0.165</v>
       </c>
       <c r="C47" t="n">
         <v>0.323</v>
       </c>
       <c r="D47" t="n">
-        <v>-0.282</v>
+        <v>-0.322</v>
       </c>
       <c r="E47" t="n">
-        <v>0.07099999999999999</v>
+        <v>-0.263</v>
       </c>
       <c r="F47" t="n">
-        <v>-0.03</v>
+        <v>-0.033</v>
       </c>
       <c r="G47" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="H47" t="n">
-        <v>-0.44</v>
+        <v>-0.78</v>
       </c>
       <c r="I47" t="n">
-        <v>0.14</v>
+        <v>-0.02</v>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>Butterfield Bermuda Championship</t>
+          <t>VidantaWorld Mexico Open</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
@@ -2362,36 +2362,36 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Peter Malnati</t>
+          <t>Johnny Keefer</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>-0.785</v>
+        <v>0.2643</v>
       </c>
       <c r="C48" t="n">
-        <v>0.323</v>
+        <v>0.26</v>
       </c>
       <c r="D48" t="n">
-        <v>-0.407</v>
+        <v>0.4029</v>
       </c>
       <c r="E48" t="n">
-        <v>0.233</v>
+        <v>0.1129</v>
       </c>
       <c r="F48" t="n">
-        <v>0.074</v>
+        <v>0.0086</v>
       </c>
       <c r="G48" t="n">
-        <v>0.2</v>
+        <v>0.02</v>
       </c>
       <c r="H48" t="n">
-        <v>-0.89</v>
+        <v>0.406</v>
       </c>
       <c r="I48" t="n">
-        <v>0.08</v>
+        <v>-0.04</v>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>Butterfield Bermuda Championship</t>
+          <t>VidantaWorld Mexico Open</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -2403,36 +2403,36 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Ben Martin</t>
+          <t>Chan Kim</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>-0.209</v>
+        <v>-0.017</v>
       </c>
       <c r="C49" t="n">
         <v>0.323</v>
       </c>
       <c r="D49" t="n">
-        <v>-0.201</v>
+        <v>-0.053</v>
       </c>
       <c r="E49" t="n">
-        <v>-0.336</v>
+        <v>-0.205</v>
       </c>
       <c r="F49" t="n">
-        <v>-0.1</v>
+        <v>0.023</v>
       </c>
       <c r="G49" t="n">
-        <v>0.04</v>
+        <v>-0.04</v>
       </c>
       <c r="H49" t="n">
-        <v>-0.85</v>
+        <v>-0.25</v>
       </c>
       <c r="I49" t="n">
         <v>0.05</v>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>Butterfield Bermuda Championship</t>
+          <t>VidantaWorld Mexico Open</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
@@ -2444,36 +2444,36 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Denny McCarthy</t>
+          <t>Tom Kim</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>-0.3471</v>
+        <v>0.216</v>
       </c>
       <c r="C50" t="n">
-        <v>0.2725</v>
+        <v>0.323</v>
       </c>
       <c r="D50" t="n">
-        <v>0.1414</v>
+        <v>0.729</v>
       </c>
       <c r="E50" t="n">
-        <v>0.5029</v>
+        <v>0.19</v>
       </c>
       <c r="F50" t="n">
-        <v>-0.0557</v>
+        <v>0.148</v>
       </c>
       <c r="G50" t="n">
-        <v>-0.03</v>
+        <v>-0.05</v>
       </c>
       <c r="H50" t="n">
-        <v>-0.0225</v>
+        <v>1.28</v>
       </c>
       <c r="I50" t="n">
         <v>-0.04</v>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>Butterfield Bermuda Championship</t>
+          <t>VidantaWorld Mexico Open</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -2485,36 +2485,36 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Max McGreevy</t>
+          <t>Patton Kizzire</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.165</v>
+        <v>-0.951</v>
       </c>
       <c r="C51" t="n">
         <v>0.323</v>
       </c>
       <c r="D51" t="n">
-        <v>0.138</v>
+        <v>-0.223</v>
       </c>
       <c r="E51" t="n">
-        <v>-0.133</v>
+        <v>-0.157</v>
       </c>
       <c r="F51" t="n">
-        <v>-0.014</v>
+        <v>0.158</v>
       </c>
       <c r="G51" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.04</v>
       </c>
       <c r="H51" t="n">
-        <v>0.16</v>
+        <v>-1.17</v>
       </c>
       <c r="I51" t="n">
-        <v>0.13</v>
+        <v>-0.02</v>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>Butterfield Bermuda Championship</t>
+          <t>VidantaWorld Mexico Open</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
@@ -2526,36 +2526,36 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Troy Merritt</t>
+          <t>Christo Lamprecht</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>-0.665</v>
+        <v>-0.342</v>
       </c>
       <c r="C52" t="n">
         <v>0.323</v>
       </c>
       <c r="D52" t="n">
-        <v>-0.587</v>
+        <v>-1.202</v>
       </c>
       <c r="E52" t="n">
-        <v>0.12</v>
+        <v>-0.029</v>
       </c>
       <c r="F52" t="n">
-        <v>-0.011</v>
+        <v>-0.005</v>
       </c>
       <c r="G52" t="n">
-        <v>0.13</v>
+        <v>0.15</v>
       </c>
       <c r="H52" t="n">
-        <v>-1.14</v>
+        <v>-1.58</v>
       </c>
       <c r="I52" t="n">
-        <v>0.04</v>
+        <v>-0.04</v>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>Butterfield Bermuda Championship</t>
+          <t>VidantaWorld Mexico Open</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
@@ -2567,36 +2567,36 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Taylor Montgomery</t>
+          <t>Hank Lebioda</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>-0.908</v>
+        <v>-0.366</v>
       </c>
       <c r="C53" t="n">
         <v>0.323</v>
       </c>
       <c r="D53" t="n">
-        <v>-0.384</v>
+        <v>-0.115</v>
       </c>
       <c r="E53" t="n">
-        <v>0.386</v>
+        <v>-0.141</v>
       </c>
       <c r="F53" t="n">
-        <v>0.176</v>
+        <v>-0.064</v>
       </c>
       <c r="G53" t="n">
-        <v>0.22</v>
+        <v>-0.02</v>
       </c>
       <c r="H53" t="n">
-        <v>-0.73</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="I53" t="n">
         <v>-0.01</v>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>Butterfield Bermuda Championship</t>
+          <t>VidantaWorld Mexico Open</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
@@ -2608,36 +2608,36 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Taylor Moore</t>
+          <t>Haotong Li</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>-0.2433</v>
+        <v>0.256</v>
       </c>
       <c r="C54" t="n">
-        <v>0.0225</v>
+        <v>0.323</v>
       </c>
       <c r="D54" t="n">
-        <v>-0.6533</v>
+        <v>0.028</v>
       </c>
       <c r="E54" t="n">
-        <v>-0.24</v>
+        <v>-0.189</v>
       </c>
       <c r="F54" t="n">
-        <v>0.09</v>
+        <v>-0.21</v>
       </c>
       <c r="G54" t="n">
-        <v>-0.01</v>
+        <v>0.06</v>
       </c>
       <c r="H54" t="n">
-        <v>-0.865</v>
+        <v>-0.12</v>
       </c>
       <c r="I54" t="n">
         <v>-0.04</v>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>Butterfield Bermuda Championship</t>
+          <t>VidantaWorld Mexico Open</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
@@ -2649,36 +2649,36 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Henrik Norlander</t>
+          <t>David Lipsky</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>-0.55</v>
+        <v>-0.242</v>
       </c>
       <c r="C55" t="n">
-        <v>0.323</v>
+        <v>0.0867</v>
       </c>
       <c r="D55" t="n">
-        <v>-0.174</v>
+        <v>-0.326</v>
       </c>
       <c r="E55" t="n">
-        <v>-0.361</v>
+        <v>0.178</v>
       </c>
       <c r="F55" t="n">
-        <v>-0.166</v>
+        <v>-0.076</v>
       </c>
       <c r="G55" t="n">
-        <v>0.1</v>
+        <v>-0.01</v>
       </c>
       <c r="H55" t="n">
-        <v>-1.25</v>
+        <v>-0.6725</v>
       </c>
       <c r="I55" t="n">
-        <v>0</v>
+        <v>-0.02</v>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>Butterfield Bermuda Championship</t>
+          <t>VidantaWorld Mexico Open</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
@@ -2690,36 +2690,36 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Andrew Novak</t>
+          <t>Justin Lower</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.238</v>
+        <v>-0.244</v>
       </c>
       <c r="C56" t="n">
         <v>0.323</v>
       </c>
       <c r="D56" t="n">
-        <v>0.393</v>
+        <v>-0.234</v>
       </c>
       <c r="E56" t="n">
-        <v>-0.217</v>
+        <v>0.015</v>
       </c>
       <c r="F56" t="n">
-        <v>0.169</v>
+        <v>-0.029</v>
       </c>
       <c r="G56" t="n">
-        <v>-0.03</v>
+        <v>-0.08</v>
       </c>
       <c r="H56" t="n">
-        <v>0.58</v>
+        <v>-0.49</v>
       </c>
       <c r="I56" t="n">
-        <v>0.08</v>
+        <v>0.04</v>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>Butterfield Bermuda Championship</t>
+          <t>VidantaWorld Mexico Open</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
@@ -2731,36 +2731,36 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Pontus Nyholm</t>
+          <t>Peter Malnati</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>-0.008</v>
+        <v>-0.6830000000000001</v>
       </c>
       <c r="C57" t="n">
         <v>0.323</v>
       </c>
       <c r="D57" t="n">
-        <v>-0.501</v>
+        <v>-0.373</v>
       </c>
       <c r="E57" t="n">
-        <v>-0.111</v>
+        <v>0.228</v>
       </c>
       <c r="F57" t="n">
-        <v>-0.12</v>
+        <v>0.045</v>
       </c>
       <c r="G57" t="n">
-        <v>0.1</v>
+        <v>-0.03</v>
       </c>
       <c r="H57" t="n">
-        <v>-0.74</v>
+        <v>-0.78</v>
       </c>
       <c r="I57" t="n">
-        <v>-0.04</v>
+        <v>-0.01</v>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>Butterfield Bermuda Championship</t>
+          <t>VidantaWorld Mexico Open</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
@@ -2772,36 +2772,36 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>John Parry</t>
+          <t>Ben Martin</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>-0.0567</v>
+        <v>-0.158</v>
       </c>
       <c r="C58" t="n">
-        <v>0.3514</v>
+        <v>0.323</v>
       </c>
       <c r="D58" t="n">
-        <v>0.3817</v>
+        <v>-0.186</v>
       </c>
       <c r="E58" t="n">
-        <v>-0.0233</v>
+        <v>-0.285</v>
       </c>
       <c r="F58" t="n">
-        <v>0.375</v>
+        <v>-0.095</v>
       </c>
       <c r="G58" t="n">
-        <v>0.01</v>
+        <v>-0.05</v>
       </c>
       <c r="H58" t="n">
-        <v>0.668</v>
+        <v>-0.72</v>
       </c>
       <c r="I58" t="n">
-        <v>-0.04</v>
+        <v>0.02</v>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>Butterfield Bermuda Championship</t>
+          <t>VidantaWorld Mexico Open</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
@@ -2813,36 +2813,36 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Jeremy Paul</t>
+          <t>Denny McCarthy</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>-0.267</v>
+        <v>-0.3471</v>
       </c>
       <c r="C59" t="n">
-        <v>0.323</v>
+        <v>0.2725</v>
       </c>
       <c r="D59" t="n">
-        <v>-0.302</v>
+        <v>0.1414</v>
       </c>
       <c r="E59" t="n">
-        <v>-0.151</v>
+        <v>0.5029</v>
       </c>
       <c r="F59" t="n">
-        <v>0.006</v>
+        <v>-0.0557</v>
       </c>
       <c r="G59" t="n">
-        <v>0.11</v>
+        <v>-0.03</v>
       </c>
       <c r="H59" t="n">
-        <v>-0.71</v>
+        <v>-0.0225</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.02</v>
+        <v>-0.04</v>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>Butterfield Bermuda Championship</t>
+          <t>VidantaWorld Mexico Open</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
@@ -2854,36 +2854,36 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Matthieu Pavon</t>
+          <t>Max McGreevy</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>-0.003</v>
+        <v>0.101</v>
       </c>
       <c r="C60" t="n">
         <v>0.323</v>
       </c>
       <c r="D60" t="n">
-        <v>-0.26</v>
+        <v>0.153</v>
       </c>
       <c r="E60" t="n">
-        <v>0.051</v>
+        <v>-0.104</v>
       </c>
       <c r="F60" t="n">
-        <v>-0.139</v>
+        <v>-0.001</v>
       </c>
       <c r="G60" t="n">
-        <v>-0.02</v>
+        <v>-0.05</v>
       </c>
       <c r="H60" t="n">
-        <v>-0.35</v>
+        <v>0.15</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.05</v>
+        <v>-0.01</v>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>Butterfield Bermuda Championship</t>
+          <t>VidantaWorld Mexico Open</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
@@ -2895,36 +2895,36 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Taylor Pendrith</t>
+          <t>Mac Meissner</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.1125</v>
+        <v>0.0314</v>
       </c>
       <c r="C61" t="n">
-        <v>0.1044</v>
+        <v>0.2288</v>
       </c>
       <c r="D61" t="n">
-        <v>-0.19</v>
+        <v>-0.2143</v>
       </c>
       <c r="E61" t="n">
-        <v>-0.38</v>
+        <v>-0.1886</v>
       </c>
       <c r="F61" t="n">
-        <v>0.0838</v>
+        <v>0.2</v>
       </c>
       <c r="G61" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="H61" t="n">
-        <v>-0.844</v>
+        <v>0.3525</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.04</v>
+        <v>-0.01</v>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>Butterfield Bermuda Championship</t>
+          <t>VidantaWorld Mexico Open</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
@@ -2936,36 +2936,36 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Paul Peterson</t>
+          <t>Taylor Moore</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>-0.517</v>
+        <v>-0.2433</v>
       </c>
       <c r="C62" t="n">
-        <v>0.323</v>
+        <v>0.0225</v>
       </c>
       <c r="D62" t="n">
-        <v>0.016</v>
+        <v>-0.6533</v>
       </c>
       <c r="E62" t="n">
-        <v>-0.05</v>
+        <v>-0.24</v>
       </c>
       <c r="F62" t="n">
-        <v>0.139</v>
+        <v>0.09</v>
       </c>
       <c r="G62" t="n">
-        <v>0.03</v>
+        <v>-0.01</v>
       </c>
       <c r="H62" t="n">
-        <v>-0.41</v>
+        <v>-0.865</v>
       </c>
       <c r="I62" t="n">
-        <v>-0.02</v>
+        <v>-0.04</v>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>Butterfield Bermuda Championship</t>
+          <t>VidantaWorld Mexico Open</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
@@ -2977,36 +2977,36 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Chandler Phillips</t>
+          <t>William Mouw</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.1567</v>
+        <v>0.051</v>
       </c>
       <c r="C63" t="n">
-        <v>0.3886</v>
+        <v>0.323</v>
       </c>
       <c r="D63" t="n">
-        <v>-0.1383</v>
+        <v>0.098</v>
       </c>
       <c r="E63" t="n">
-        <v>0.3417</v>
+        <v>0.002</v>
       </c>
       <c r="F63" t="n">
-        <v>0.5983000000000001</v>
+        <v>-0.052</v>
       </c>
       <c r="G63" t="n">
-        <v>-0.01</v>
+        <v>0.03</v>
       </c>
       <c r="H63" t="n">
-        <v>0.61</v>
+        <v>0.1</v>
       </c>
       <c r="I63" t="n">
-        <v>-0.04</v>
+        <v>-0.03</v>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>Butterfield Bermuda Championship</t>
+          <t>VidantaWorld Mexico Open</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
@@ -3018,36 +3018,36 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Aldrich Potgieter</t>
+          <t>Keita Nakajima</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.2</v>
+        <v>0.27</v>
       </c>
       <c r="C64" t="n">
-        <v>0</v>
+        <v>0.2683</v>
       </c>
       <c r="D64" t="n">
-        <v>-0.7633</v>
+        <v>0.43</v>
       </c>
       <c r="E64" t="n">
-        <v>0.1167</v>
+        <v>0.206</v>
       </c>
       <c r="F64" t="n">
-        <v>-0.6833</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="G64" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="H64" t="n">
-        <v>-1.878</v>
+        <v>0.255</v>
       </c>
       <c r="I64" t="n">
         <v>-0.01</v>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>Butterfield Bermuda Championship</t>
+          <t>VidantaWorld Mexico Open</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
@@ -3059,36 +3059,36 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Seamus Power</t>
+          <t>Rasmus Neergaard-Petersen</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>-0.093</v>
+        <v>0.71</v>
       </c>
       <c r="C65" t="n">
-        <v>0.323</v>
+        <v>0.29</v>
       </c>
       <c r="D65" t="n">
-        <v>-0.274</v>
+        <v>0.102</v>
       </c>
       <c r="E65" t="n">
-        <v>0.346</v>
+        <v>-0.426</v>
       </c>
       <c r="F65" t="n">
-        <v>0.222</v>
+        <v>-0.026</v>
       </c>
       <c r="G65" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="H65" t="n">
-        <v>0.2</v>
+        <v>0.4925</v>
       </c>
       <c r="I65" t="n">
-        <v>0.2</v>
+        <v>-0.04</v>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>Butterfield Bermuda Championship</t>
+          <t>VidantaWorld Mexico Open</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
@@ -3100,36 +3100,36 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Chad Ramey</t>
+          <t>Andrew Novak</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>-0.252</v>
+        <v>0.192</v>
       </c>
       <c r="C66" t="n">
         <v>0.323</v>
       </c>
       <c r="D66" t="n">
-        <v>-0.276</v>
+        <v>0.455</v>
       </c>
       <c r="E66" t="n">
-        <v>0.24</v>
+        <v>-0.217</v>
       </c>
       <c r="F66" t="n">
-        <v>0.137</v>
+        <v>0.158</v>
       </c>
       <c r="G66" t="n">
-        <v>0.04</v>
+        <v>0</v>
       </c>
       <c r="H66" t="n">
-        <v>-0.15</v>
+        <v>0.59</v>
       </c>
       <c r="I66" t="n">
-        <v>-0</v>
+        <v>0.09</v>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>Butterfield Bermuda Championship</t>
+          <t>VidantaWorld Mexico Open</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
@@ -3141,36 +3141,36 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Davis Riley</t>
+          <t>Pontus Nyholm</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>-0.516</v>
+        <v>0.013</v>
       </c>
       <c r="C67" t="n">
         <v>0.323</v>
       </c>
       <c r="D67" t="n">
-        <v>-0.45</v>
+        <v>-0.511</v>
       </c>
       <c r="E67" t="n">
-        <v>0.383</v>
+        <v>-0.149</v>
       </c>
       <c r="F67" t="n">
-        <v>-0.11</v>
+        <v>-0.1</v>
       </c>
       <c r="G67" t="n">
-        <v>0.15</v>
+        <v>0.13</v>
       </c>
       <c r="H67" t="n">
-        <v>-0.6899999999999999</v>
+        <v>-0.75</v>
       </c>
       <c r="I67" t="n">
-        <v>0.03</v>
+        <v>-0.04</v>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>Butterfield Bermuda Championship</t>
+          <t>VidantaWorld Mexico Open</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
@@ -3182,36 +3182,36 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Kevin Roy</t>
+          <t>John Parry</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.4643</v>
+        <v>-0.0567</v>
       </c>
       <c r="C68" t="n">
-        <v>0.3575</v>
+        <v>0.3514</v>
       </c>
       <c r="D68" t="n">
-        <v>0.1929</v>
+        <v>0.3817</v>
       </c>
       <c r="E68" t="n">
-        <v>-0.2471</v>
+        <v>-0.0233</v>
       </c>
       <c r="F68" t="n">
-        <v>-0.0871</v>
+        <v>0.375</v>
       </c>
       <c r="G68" t="n">
         <v>0.01</v>
       </c>
       <c r="H68" t="n">
-        <v>1.332</v>
+        <v>0.668</v>
       </c>
       <c r="I68" t="n">
-        <v>-0.02</v>
+        <v>-0.04</v>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>Butterfield Bermuda Championship</t>
+          <t>VidantaWorld Mexico Open</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
@@ -3223,36 +3223,36 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Marcelo Rozo</t>
+          <t>Matthieu Pavon</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>-0.168</v>
+        <v>0.017</v>
       </c>
       <c r="C69" t="n">
         <v>0.323</v>
       </c>
       <c r="D69" t="n">
-        <v>-0.62</v>
+        <v>-0.247</v>
       </c>
       <c r="E69" t="n">
-        <v>-0.451</v>
+        <v>-0.055</v>
       </c>
       <c r="F69" t="n">
-        <v>-0.381</v>
+        <v>-0.145</v>
       </c>
       <c r="G69" t="n">
-        <v>0.04</v>
+        <v>0.01</v>
       </c>
       <c r="H69" t="n">
-        <v>-1.62</v>
+        <v>-0.43</v>
       </c>
       <c r="I69" t="n">
         <v>-0.04</v>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>Butterfield Bermuda Championship</t>
+          <t>VidantaWorld Mexico Open</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
@@ -3264,36 +3264,36 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Isaiah Salinda</t>
+          <t>Taylor Pendrith</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.166</v>
+        <v>0.1125</v>
       </c>
       <c r="C70" t="n">
-        <v>0.323</v>
+        <v>0.1044</v>
       </c>
       <c r="D70" t="n">
-        <v>-0.231</v>
+        <v>-0.19</v>
       </c>
       <c r="E70" t="n">
-        <v>-0.451</v>
+        <v>-0.38</v>
       </c>
       <c r="F70" t="n">
-        <v>-0.232</v>
+        <v>0.0838</v>
       </c>
       <c r="G70" t="n">
-        <v>-0.03</v>
+        <v>0</v>
       </c>
       <c r="H70" t="n">
-        <v>-0.75</v>
+        <v>-0.844</v>
       </c>
       <c r="I70" t="n">
-        <v>0</v>
+        <v>-0.04</v>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>Butterfield Bermuda Championship</t>
+          <t>VidantaWorld Mexico Open</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
@@ -3305,36 +3305,36 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Adam Schenk</t>
+          <t>Marco Penge</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>-0.484</v>
+        <v>0.318</v>
       </c>
       <c r="C71" t="n">
         <v>0.323</v>
       </c>
       <c r="D71" t="n">
-        <v>-0.576</v>
+        <v>0.027</v>
       </c>
       <c r="E71" t="n">
-        <v>-0.058</v>
+        <v>0.042</v>
       </c>
       <c r="F71" t="n">
-        <v>-0.014</v>
+        <v>-0.03</v>
       </c>
       <c r="G71" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="H71" t="n">
-        <v>-1.13</v>
+        <v>0.36</v>
       </c>
       <c r="I71" t="n">
-        <v>0.09</v>
+        <v>-0.04</v>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>Butterfield Bermuda Championship</t>
+          <t>VidantaWorld Mexico Open</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
@@ -3346,36 +3346,36 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Neal Shipley</t>
+          <t>Paul Peterson</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.627</v>
+        <v>-0.502</v>
       </c>
       <c r="C72" t="n">
         <v>0.323</v>
       </c>
       <c r="D72" t="n">
-        <v>0.172</v>
+        <v>0.007</v>
       </c>
       <c r="E72" t="n">
-        <v>-0.192</v>
+        <v>-0.08</v>
       </c>
       <c r="F72" t="n">
-        <v>-0.193</v>
+        <v>0.107</v>
       </c>
       <c r="G72" t="n">
-        <v>-0.14</v>
+        <v>-0.19</v>
       </c>
       <c r="H72" t="n">
-        <v>0.41</v>
+        <v>-0.47</v>
       </c>
       <c r="I72" t="n">
-        <v>-0.04</v>
+        <v>-0.05</v>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>Butterfield Bermuda Championship</t>
+          <t>VidantaWorld Mexico Open</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
@@ -3387,36 +3387,36 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Greyson Sigg</t>
+          <t>Chandler Phillips</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>-0.259</v>
+        <v>0.1567</v>
       </c>
       <c r="C73" t="n">
-        <v>0.323</v>
+        <v>0.3886</v>
       </c>
       <c r="D73" t="n">
-        <v>0.022</v>
+        <v>-0.1383</v>
       </c>
       <c r="E73" t="n">
-        <v>-0.301</v>
+        <v>0.3417</v>
       </c>
       <c r="F73" t="n">
-        <v>0.003</v>
+        <v>0.5983000000000001</v>
       </c>
       <c r="G73" t="n">
-        <v>0.04</v>
+        <v>-0.01</v>
       </c>
       <c r="H73" t="n">
-        <v>-0.54</v>
+        <v>0.61</v>
       </c>
       <c r="I73" t="n">
-        <v>0.09</v>
+        <v>-0.04</v>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>Butterfield Bermuda Championship</t>
+          <t>VidantaWorld Mexico Open</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
@@ -3428,36 +3428,36 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Ben Silverman</t>
+          <t>Aldrich Potgieter</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>-0.219</v>
+        <v>0.2</v>
       </c>
       <c r="C74" t="n">
-        <v>0.323</v>
+        <v>0</v>
       </c>
       <c r="D74" t="n">
-        <v>-0.353</v>
+        <v>-0.7633</v>
       </c>
       <c r="E74" t="n">
-        <v>0.064</v>
+        <v>0.1167</v>
       </c>
       <c r="F74" t="n">
-        <v>-0.034</v>
+        <v>-0.6833</v>
       </c>
       <c r="G74" t="n">
-        <v>0.05</v>
+        <v>0.01</v>
       </c>
       <c r="H74" t="n">
-        <v>-0.54</v>
+        <v>-1.878</v>
       </c>
       <c r="I74" t="n">
-        <v>-0.05</v>
+        <v>-0.01</v>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>Butterfield Bermuda Championship</t>
+          <t>VidantaWorld Mexico Open</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
@@ -3469,36 +3469,36 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>David Skinns</t>
+          <t>Andrew Putnam</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>-0.667</v>
+        <v>-0.89</v>
       </c>
       <c r="C75" t="n">
-        <v>0.323</v>
+        <v>0</v>
       </c>
       <c r="D75" t="n">
-        <v>-0.124</v>
+        <v>0.195</v>
       </c>
       <c r="E75" t="n">
-        <v>-0.195</v>
+        <v>0.2667</v>
       </c>
       <c r="F75" t="n">
-        <v>0.06900000000000001</v>
+        <v>0.0733</v>
       </c>
       <c r="G75" t="n">
-        <v>0.13</v>
+        <v>-0.02</v>
       </c>
       <c r="H75" t="n">
-        <v>-0.92</v>
+        <v>-0.0825</v>
       </c>
       <c r="I75" t="n">
-        <v>0.03</v>
+        <v>-0.05</v>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>Butterfield Bermuda Championship</t>
+          <t>VidantaWorld Mexico Open</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
@@ -3510,36 +3510,36 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Austin Smotherman</t>
+          <t>Chad Ramey</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.424</v>
+        <v>-0.253</v>
       </c>
       <c r="C76" t="n">
         <v>0.323</v>
       </c>
       <c r="D76" t="n">
-        <v>0.492</v>
+        <v>-0.269</v>
       </c>
       <c r="E76" t="n">
-        <v>-0.238</v>
+        <v>0.197</v>
       </c>
       <c r="F76" t="n">
-        <v>-0.214</v>
+        <v>0.111</v>
       </c>
       <c r="G76" t="n">
-        <v>-0.12</v>
+        <v>-0.03</v>
       </c>
       <c r="H76" t="n">
-        <v>0.46</v>
+        <v>-0.21</v>
       </c>
       <c r="I76" t="n">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>Butterfield Bermuda Championship</t>
+          <t>VidantaWorld Mexico Open</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
@@ -3551,36 +3551,36 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Hayden Springer</t>
+          <t>Davis Riley</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>-0.122</v>
+        <v>-0.425</v>
       </c>
       <c r="C77" t="n">
         <v>0.323</v>
       </c>
       <c r="D77" t="n">
-        <v>-0.27</v>
+        <v>-0.368</v>
       </c>
       <c r="E77" t="n">
-        <v>0.218</v>
+        <v>0.335</v>
       </c>
       <c r="F77" t="n">
-        <v>-0.049</v>
+        <v>-0.137</v>
       </c>
       <c r="G77" t="n">
-        <v>0.06</v>
+        <v>0.03</v>
       </c>
       <c r="H77" t="n">
-        <v>-0.22</v>
+        <v>-0.59</v>
       </c>
       <c r="I77" t="n">
-        <v>0.02</v>
+        <v>0.04</v>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>Butterfield Bermuda Championship</t>
+          <t>VidantaWorld Mexico Open</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
@@ -3592,36 +3592,36 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Jimmy Stanger</t>
+          <t>Patrick Rodgers</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>-0.039</v>
+        <v>-0.574</v>
       </c>
       <c r="C78" t="n">
-        <v>0.323</v>
+        <v>0.06</v>
       </c>
       <c r="D78" t="n">
-        <v>-0.8129999999999999</v>
+        <v>-0.724</v>
       </c>
       <c r="E78" t="n">
-        <v>-0.125</v>
+        <v>-0.05</v>
       </c>
       <c r="F78" t="n">
-        <v>-0.117</v>
+        <v>-0.016</v>
       </c>
       <c r="G78" t="n">
-        <v>0.07000000000000001</v>
+        <v>-0.02</v>
       </c>
       <c r="H78" t="n">
-        <v>-1.09</v>
+        <v>-1.27</v>
       </c>
       <c r="I78" t="n">
         <v>-0.04</v>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>Butterfield Bermuda Championship</t>
+          <t>VidantaWorld Mexico Open</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
@@ -3633,36 +3633,36 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Kevin Streelman</t>
+          <t>Kevin Roy</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>-0.063</v>
+        <v>0.4643</v>
       </c>
       <c r="C79" t="n">
-        <v>0.323</v>
+        <v>0.3575</v>
       </c>
       <c r="D79" t="n">
-        <v>-0.125</v>
+        <v>0.1929</v>
       </c>
       <c r="E79" t="n">
-        <v>0.081</v>
+        <v>-0.2471</v>
       </c>
       <c r="F79" t="n">
-        <v>-0.035</v>
+        <v>-0.0871</v>
       </c>
       <c r="G79" t="n">
         <v>0.01</v>
       </c>
       <c r="H79" t="n">
-        <v>-0.14</v>
+        <v>1.332</v>
       </c>
       <c r="I79" t="n">
-        <v>-0.05</v>
+        <v>-0.02</v>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>Butterfield Bermuda Championship</t>
+          <t>VidantaWorld Mexico Open</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
@@ -3674,36 +3674,36 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Adam Svensson</t>
+          <t>Marcelo Rozo</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>-0.401</v>
+        <v>-0.164</v>
       </c>
       <c r="C80" t="n">
         <v>0.323</v>
       </c>
       <c r="D80" t="n">
-        <v>0.117</v>
+        <v>-0.618</v>
       </c>
       <c r="E80" t="n">
-        <v>-0.364</v>
+        <v>-0.436</v>
       </c>
       <c r="F80" t="n">
-        <v>0.013</v>
+        <v>-0.319</v>
       </c>
       <c r="G80" t="n">
-        <v>0.06</v>
+        <v>-0.05</v>
       </c>
       <c r="H80" t="n">
-        <v>-0.63</v>
+        <v>-1.54</v>
       </c>
       <c r="I80" t="n">
-        <v>-0</v>
+        <v>-0.04</v>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>Butterfield Bermuda Championship</t>
+          <t>VidantaWorld Mexico Open</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
@@ -3715,36 +3715,36 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Jesper Svensson</t>
+          <t>Isaiah Salinda</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.369</v>
+        <v>0.287</v>
       </c>
       <c r="C81" t="n">
         <v>0.323</v>
       </c>
       <c r="D81" t="n">
-        <v>-0.369</v>
+        <v>-0.113</v>
       </c>
       <c r="E81" t="n">
-        <v>-0.182</v>
+        <v>-0.459</v>
       </c>
       <c r="F81" t="n">
-        <v>-0.154</v>
+        <v>-0.184</v>
       </c>
       <c r="G81" t="n">
-        <v>-0.02</v>
+        <v>0.09</v>
       </c>
       <c r="H81" t="n">
-        <v>-0.34</v>
+        <v>-0.47</v>
       </c>
       <c r="I81" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>Butterfield Bermuda Championship</t>
+          <t>VidantaWorld Mexico Open</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
@@ -3756,36 +3756,36 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Davis Thompson</t>
+          <t>Gordon Sargent</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.1833</v>
+        <v>0.225</v>
       </c>
       <c r="C82" t="n">
-        <v>0.4629</v>
+        <v>0.323</v>
       </c>
       <c r="D82" t="n">
-        <v>0.7483</v>
+        <v>-0.445</v>
       </c>
       <c r="E82" t="n">
-        <v>-0.1183</v>
+        <v>0.029</v>
       </c>
       <c r="F82" t="n">
-        <v>-0.2583</v>
+        <v>0.056</v>
       </c>
       <c r="G82" t="n">
-        <v>0.02</v>
+        <v>0.15</v>
       </c>
       <c r="H82" t="n">
-        <v>0.8725000000000001</v>
+        <v>-0.14</v>
       </c>
       <c r="I82" t="n">
         <v>-0.04</v>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>Butterfield Bermuda Championship</t>
+          <t>VidantaWorld Mexico Open</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
@@ -3797,36 +3797,36 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Alejandro Tosti</t>
+          <t>Neal Shipley</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.15</v>
+        <v>0.606</v>
       </c>
       <c r="C83" t="n">
         <v>0.323</v>
       </c>
       <c r="D83" t="n">
-        <v>-0.397</v>
+        <v>0.162</v>
       </c>
       <c r="E83" t="n">
-        <v>-0.371</v>
+        <v>-0.168</v>
       </c>
       <c r="F83" t="n">
-        <v>-0.038</v>
+        <v>-0.174</v>
       </c>
       <c r="G83" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="H83" t="n">
-        <v>-0.66</v>
+        <v>0.43</v>
       </c>
       <c r="I83" t="n">
         <v>-0.04</v>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>Butterfield Bermuda Championship</t>
+          <t>VidantaWorld Mexico Open</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
@@ -3838,36 +3838,36 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Erik Van Rooyen</t>
+          <t>Ben Silverman</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>-0.074</v>
+        <v>-0.141</v>
       </c>
       <c r="C84" t="n">
         <v>0.323</v>
       </c>
       <c r="D84" t="n">
-        <v>-0.305</v>
+        <v>-0.191</v>
       </c>
       <c r="E84" t="n">
         <v>0.056</v>
       </c>
       <c r="F84" t="n">
-        <v>-0.012</v>
+        <v>-0.025</v>
       </c>
       <c r="G84" t="n">
-        <v>0.06</v>
+        <v>-0.08</v>
       </c>
       <c r="H84" t="n">
-        <v>-0.34</v>
+        <v>-0.3</v>
       </c>
       <c r="I84" t="n">
-        <v>-0.01</v>
+        <v>0.02</v>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>Butterfield Bermuda Championship</t>
+          <t>VidantaWorld Mexico Open</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
@@ -3879,36 +3879,36 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>John VanDerLaan</t>
+          <t>David Skinns</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.06</v>
+        <v>-0.585</v>
       </c>
       <c r="C85" t="n">
         <v>0.323</v>
       </c>
       <c r="D85" t="n">
-        <v>-0.139</v>
+        <v>-0.07099999999999999</v>
       </c>
       <c r="E85" t="n">
-        <v>-0.189</v>
+        <v>-0.191</v>
       </c>
       <c r="F85" t="n">
-        <v>0.002</v>
+        <v>0.109</v>
       </c>
       <c r="G85" t="n">
         <v>-0.01</v>
       </c>
       <c r="H85" t="n">
-        <v>-0.27</v>
+        <v>-0.74</v>
       </c>
       <c r="I85" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>Butterfield Bermuda Championship</t>
+          <t>VidantaWorld Mexico Open</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
@@ -3920,36 +3920,36 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Kristoffer Ventura</t>
+          <t>Jordan Smith</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.481</v>
+        <v>0.58</v>
       </c>
       <c r="C86" t="n">
-        <v>0.323</v>
+        <v>0.675</v>
       </c>
       <c r="D86" t="n">
-        <v>0.06</v>
+        <v>0.294</v>
       </c>
       <c r="E86" t="n">
-        <v>-0.08799999999999999</v>
+        <v>0.186</v>
       </c>
       <c r="F86" t="n">
-        <v>-0.053</v>
+        <v>-0.266</v>
       </c>
       <c r="G86" t="n">
-        <v>-0.09</v>
+        <v>0.03</v>
       </c>
       <c r="H86" t="n">
-        <v>0.4</v>
+        <v>1.278</v>
       </c>
       <c r="I86" t="n">
-        <v>0.01</v>
+        <v>-0.04</v>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>Butterfield Bermuda Championship</t>
+          <t>VidantaWorld Mexico Open</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
@@ -3961,36 +3961,36 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Camilo Villegas</t>
+          <t>Hayden Springer</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>-0.996</v>
+        <v>-0.273</v>
       </c>
       <c r="C87" t="n">
         <v>0.323</v>
       </c>
       <c r="D87" t="n">
-        <v>-0.488</v>
+        <v>-0.255</v>
       </c>
       <c r="E87" t="n">
-        <v>0.032</v>
+        <v>0.298</v>
       </c>
       <c r="F87" t="n">
-        <v>0.039</v>
+        <v>-0.008999999999999999</v>
       </c>
       <c r="G87" t="n">
-        <v>0.26</v>
+        <v>0.05</v>
       </c>
       <c r="H87" t="n">
-        <v>-1.41</v>
+        <v>-0.24</v>
       </c>
       <c r="I87" t="n">
-        <v>0.22</v>
+        <v>0.02</v>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>Butterfield Bermuda Championship</t>
+          <t>VidantaWorld Mexico Open</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
@@ -4002,36 +4002,36 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Danny Walker</t>
+          <t>Jimmy Stanger</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>-0.142</v>
+        <v>-0.037</v>
       </c>
       <c r="C88" t="n">
         <v>0.323</v>
       </c>
       <c r="D88" t="n">
-        <v>-0.249</v>
+        <v>-0.787</v>
       </c>
       <c r="E88" t="n">
-        <v>-0.183</v>
+        <v>-0.11</v>
       </c>
       <c r="F88" t="n">
-        <v>-0.06</v>
+        <v>-0.139</v>
       </c>
       <c r="G88" t="n">
-        <v>0.1</v>
+        <v>0.08</v>
       </c>
       <c r="H88" t="n">
-        <v>-0.63</v>
+        <v>-1.07</v>
       </c>
       <c r="I88" t="n">
-        <v>-0.04</v>
+        <v>-0</v>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>Butterfield Bermuda Championship</t>
+          <t>VidantaWorld Mexico Open</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
@@ -4043,36 +4043,36 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Vince Whaley</t>
+          <t>Kevin Streelman</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>-0.858</v>
+        <v>-0.07199999999999999</v>
       </c>
       <c r="C89" t="n">
         <v>0.323</v>
       </c>
       <c r="D89" t="n">
-        <v>-0.624</v>
+        <v>-0.179</v>
       </c>
       <c r="E89" t="n">
-        <v>0.352</v>
+        <v>0.039</v>
       </c>
       <c r="F89" t="n">
-        <v>0.174</v>
+        <v>-0.074</v>
       </c>
       <c r="G89" t="n">
-        <v>0.22</v>
+        <v>-0.06</v>
       </c>
       <c r="H89" t="n">
-        <v>-0.96</v>
+        <v>-0.28</v>
       </c>
       <c r="I89" t="n">
-        <v>0.16</v>
+        <v>-0.04</v>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>Butterfield Bermuda Championship</t>
+          <t>VidantaWorld Mexico Open</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
@@ -4084,36 +4084,36 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Aaron Wise</t>
+          <t>Jackson Suber</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>-0.324</v>
+        <v>0.1671</v>
       </c>
       <c r="C90" t="n">
-        <v>0.323</v>
+        <v>0.54</v>
       </c>
       <c r="D90" t="n">
-        <v>-0.275</v>
+        <v>0.5814</v>
       </c>
       <c r="E90" t="n">
-        <v>-0.179</v>
+        <v>-0.0571</v>
       </c>
       <c r="F90" t="n">
+        <v>0.3814</v>
+      </c>
+      <c r="G90" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="H90" t="n">
+        <v>0.6475</v>
+      </c>
+      <c r="I90" t="n">
         <v>-0.04</v>
       </c>
-      <c r="G90" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="H90" t="n">
-        <v>-0.82</v>
-      </c>
-      <c r="I90" t="n">
-        <v>0.05</v>
-      </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>Butterfield Bermuda Championship</t>
+          <t>VidantaWorld Mexico Open</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
@@ -4125,36 +4125,36 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Dylan Wu</t>
+          <t>Adam Svensson</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>-0.371</v>
+        <v>-0.358</v>
       </c>
       <c r="C91" t="n">
         <v>0.323</v>
       </c>
       <c r="D91" t="n">
-        <v>-0.228</v>
+        <v>0.104</v>
       </c>
       <c r="E91" t="n">
-        <v>0.08599999999999999</v>
+        <v>-0.383</v>
       </c>
       <c r="F91" t="n">
-        <v>0.06</v>
+        <v>0.027</v>
       </c>
       <c r="G91" t="n">
-        <v>0.08</v>
+        <v>-0.06</v>
       </c>
       <c r="H91" t="n">
-        <v>-0.45</v>
+        <v>-0.61</v>
       </c>
       <c r="I91" t="n">
-        <v>0.1</v>
+        <v>-0.04</v>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>Butterfield Bermuda Championship</t>
+          <t>VidantaWorld Mexico Open</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
@@ -4166,39 +4166,531 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
+          <t>Jesper Svensson</t>
+        </is>
+      </c>
+      <c r="B92" t="n">
+        <v>0.388</v>
+      </c>
+      <c r="C92" t="n">
+        <v>0.323</v>
+      </c>
+      <c r="D92" t="n">
+        <v>-0.325</v>
+      </c>
+      <c r="E92" t="n">
+        <v>-0.148</v>
+      </c>
+      <c r="F92" t="n">
+        <v>-0.148</v>
+      </c>
+      <c r="G92" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="H92" t="n">
+        <v>-0.23</v>
+      </c>
+      <c r="I92" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>VidantaWorld Mexico Open</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>PGA Tour</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Alejandro Tosti</t>
+        </is>
+      </c>
+      <c r="B93" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="C93" t="n">
+        <v>0.323</v>
+      </c>
+      <c r="D93" t="n">
+        <v>-0.429</v>
+      </c>
+      <c r="E93" t="n">
+        <v>-0.324</v>
+      </c>
+      <c r="F93" t="n">
+        <v>-0.001</v>
+      </c>
+      <c r="G93" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="H93" t="n">
+        <v>-0.67</v>
+      </c>
+      <c r="I93" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>VidantaWorld Mexico Open</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>PGA Tour</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Erik Van Rooyen</t>
+        </is>
+      </c>
+      <c r="B94" t="n">
+        <v>-0.07099999999999999</v>
+      </c>
+      <c r="C94" t="n">
+        <v>0.323</v>
+      </c>
+      <c r="D94" t="n">
+        <v>-0.394</v>
+      </c>
+      <c r="E94" t="n">
+        <v>0.073</v>
+      </c>
+      <c r="F94" t="n">
+        <v>0.016</v>
+      </c>
+      <c r="G94" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="H94" t="n">
+        <v>-0.38</v>
+      </c>
+      <c r="I94" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>VidantaWorld Mexico Open</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>PGA Tour</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>John VanDerLaan</t>
+        </is>
+      </c>
+      <c r="B95" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="C95" t="n">
+        <v>0.323</v>
+      </c>
+      <c r="D95" t="n">
+        <v>-0.158</v>
+      </c>
+      <c r="E95" t="n">
+        <v>-0.208</v>
+      </c>
+      <c r="F95" t="n">
+        <v>-0.019</v>
+      </c>
+      <c r="G95" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="H95" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="I95" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>VidantaWorld Mexico Open</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>PGA Tour</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Kristoffer Ventura</t>
+        </is>
+      </c>
+      <c r="B96" t="n">
+        <v>0.462</v>
+      </c>
+      <c r="C96" t="n">
+        <v>0.323</v>
+      </c>
+      <c r="D96" t="n">
+        <v>0.008999999999999999</v>
+      </c>
+      <c r="E96" t="n">
+        <v>-0.054</v>
+      </c>
+      <c r="F96" t="n">
+        <v>-0.064</v>
+      </c>
+      <c r="G96" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="H96" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="I96" t="n">
+        <v>-0</v>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>VidantaWorld Mexico Open</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>PGA Tour</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Karl Vilips</t>
+        </is>
+      </c>
+      <c r="B97" t="n">
+        <v>-0.118</v>
+      </c>
+      <c r="C97" t="n">
+        <v>0.323</v>
+      </c>
+      <c r="D97" t="n">
+        <v>0.083</v>
+      </c>
+      <c r="E97" t="n">
+        <v>0.029</v>
+      </c>
+      <c r="F97" t="n">
+        <v>-0.036</v>
+      </c>
+      <c r="G97" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="H97" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="I97" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>VidantaWorld Mexico Open</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>PGA Tour</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Camilo Villegas</t>
+        </is>
+      </c>
+      <c r="B98" t="n">
+        <v>-1.016</v>
+      </c>
+      <c r="C98" t="n">
+        <v>0.323</v>
+      </c>
+      <c r="D98" t="n">
+        <v>-0.492</v>
+      </c>
+      <c r="E98" t="n">
+        <v>0.019</v>
+      </c>
+      <c r="F98" t="n">
+        <v>0.023</v>
+      </c>
+      <c r="G98" t="n">
+        <v>-0.07000000000000001</v>
+      </c>
+      <c r="H98" t="n">
+        <v>-1.47</v>
+      </c>
+      <c r="I98" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>VidantaWorld Mexico Open</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>PGA Tour</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Danny Walker</t>
+        </is>
+      </c>
+      <c r="B99" t="n">
+        <v>-0.111</v>
+      </c>
+      <c r="C99" t="n">
+        <v>0.323</v>
+      </c>
+      <c r="D99" t="n">
+        <v>-0.175</v>
+      </c>
+      <c r="E99" t="n">
+        <v>-0.118</v>
+      </c>
+      <c r="F99" t="n">
+        <v>-0.063</v>
+      </c>
+      <c r="G99" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="H99" t="n">
+        <v>-0.47</v>
+      </c>
+      <c r="I99" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>VidantaWorld Mexico Open</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>PGA Tour</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Vince Whaley</t>
+        </is>
+      </c>
+      <c r="B100" t="n">
+        <v>-0.89</v>
+      </c>
+      <c r="C100" t="n">
+        <v>0.323</v>
+      </c>
+      <c r="D100" t="n">
+        <v>-0.726</v>
+      </c>
+      <c r="E100" t="n">
+        <v>0.405</v>
+      </c>
+      <c r="F100" t="n">
+        <v>0.202</v>
+      </c>
+      <c r="G100" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="H100" t="n">
+        <v>-1.01</v>
+      </c>
+      <c r="I100" t="n">
+        <v>-0.07000000000000001</v>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>VidantaWorld Mexico Open</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>PGA Tour</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Aaron Wise</t>
+        </is>
+      </c>
+      <c r="B101" t="n">
+        <v>-0.417</v>
+      </c>
+      <c r="C101" t="n">
+        <v>0.323</v>
+      </c>
+      <c r="D101" t="n">
+        <v>-0.315</v>
+      </c>
+      <c r="E101" t="n">
+        <v>-0.118</v>
+      </c>
+      <c r="F101" t="n">
+        <v>-0.044</v>
+      </c>
+      <c r="G101" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="H101" t="n">
+        <v>-0.9</v>
+      </c>
+      <c r="I101" t="n">
+        <v>0</v>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>VidantaWorld Mexico Open</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>PGA Tour</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Dylan Wu</t>
+        </is>
+      </c>
+      <c r="B102" t="n">
+        <v>-0.345</v>
+      </c>
+      <c r="C102" t="n">
+        <v>0.323</v>
+      </c>
+      <c r="D102" t="n">
+        <v>-0.155</v>
+      </c>
+      <c r="E102" t="n">
+        <v>0.063</v>
+      </c>
+      <c r="F102" t="n">
+        <v>0.097</v>
+      </c>
+      <c r="G102" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="H102" t="n">
+        <v>-0.34</v>
+      </c>
+      <c r="I102" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>VidantaWorld Mexico Open</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>PGA Tour</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Sudarshan Yellamaraju</t>
+        </is>
+      </c>
+      <c r="B103" t="n">
+        <v>0.263</v>
+      </c>
+      <c r="C103" t="n">
+        <v>0.323</v>
+      </c>
+      <c r="D103" t="n">
+        <v>0.043</v>
+      </c>
+      <c r="E103" t="n">
+        <v>-0.192</v>
+      </c>
+      <c r="F103" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="G103" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H103" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I103" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>VidantaWorld Mexico Open</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>PGA Tour</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
           <t>Kevin Yu</t>
         </is>
       </c>
-      <c r="B92" t="n">
+      <c r="B104" t="n">
         <v>0.4867</v>
       </c>
-      <c r="C92" t="n">
+      <c r="C104" t="n">
         <v>0.4171</v>
       </c>
-      <c r="D92" t="n">
+      <c r="D104" t="n">
         <v>0.4867</v>
       </c>
-      <c r="E92" t="n">
+      <c r="E104" t="n">
         <v>0.1667</v>
       </c>
-      <c r="F92" t="n">
+      <c r="F104" t="n">
         <v>0.1</v>
       </c>
-      <c r="G92" t="n">
+      <c r="G104" t="n">
         <v>0.02</v>
       </c>
-      <c r="H92" t="n">
+      <c r="H104" t="n">
         <v>0.896</v>
       </c>
-      <c r="I92" t="n">
+      <c r="I104" t="n">
         <v>-0.01</v>
       </c>
-      <c r="J92" t="inlineStr">
-        <is>
-          <t>Butterfield Bermuda Championship</t>
-        </is>
-      </c>
-      <c r="K92" t="inlineStr">
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>VidantaWorld Mexico Open</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr">
         <is>
           <t>PGA Tour</t>
         </is>
